--- a/planilhas/veiculos.xlsx
+++ b/planilhas/veiculos.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$AU$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$AU$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$AU$46</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
   <si>
     <t>Veículos por contrato de locação</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 14 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quinta-feira, 21 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Código do veículo</t>
@@ -202,7 +202,7 @@
     <t>9BWAG45U5LT080519</t>
   </si>
   <si>
-    <t>221704</t>
+    <t>222685</t>
   </si>
   <si>
     <t/>
@@ -223,1203 +223,1227 @@
     <t>EM UTILIZAÇÃO</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>LOCADORA</t>
+  </si>
+  <si>
+    <t>LOCADO</t>
+  </si>
+  <si>
+    <t>ALIENADO</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: GOL 1.0L MC4</t>
+  </si>
+  <si>
+    <t>CTO-1077</t>
+  </si>
+  <si>
+    <t>MOTORISTA DE APLICATIVO</t>
+  </si>
+  <si>
+    <t>LOC-1077-1/4</t>
+  </si>
+  <si>
+    <t>097.034.444-90</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
+    <t>QGT-6I05</t>
+  </si>
+  <si>
+    <t>1199692430</t>
+  </si>
+  <si>
+    <t>9BWAG45U9LT036412</t>
+  </si>
+  <si>
+    <t>213594</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>CTO-1081</t>
+  </si>
+  <si>
+    <t>LOC-1081-1/12</t>
+  </si>
+  <si>
+    <t>014.009.964-65</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>QGX-7353</t>
+  </si>
+  <si>
+    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>005455-0</t>
+  </si>
+  <si>
+    <t>1149589393</t>
+  </si>
+  <si>
+    <t>9BWAG45UXJT141960</t>
+  </si>
+  <si>
+    <t>177643</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/NOVO GOL TL MCV</t>
+  </si>
+  <si>
+    <t>CTO-1028</t>
+  </si>
+  <si>
+    <t>LOC-1028-1/8</t>
+  </si>
+  <si>
+    <t>120.205.544-37</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>RGE-5D51</t>
+  </si>
+  <si>
+    <t>1253118830</t>
+  </si>
+  <si>
+    <t>9BWAG45UXMT107456</t>
+  </si>
+  <si>
+    <t>191102</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/GOL 1.0L MC4</t>
+  </si>
+  <si>
+    <t>CTO-1010</t>
+  </si>
+  <si>
+    <t>LOC-1010-1/9</t>
+  </si>
+  <si>
+    <t>700.139.284-73</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>RGE-7G92</t>
+  </si>
+  <si>
+    <t>1253913371</t>
+  </si>
+  <si>
+    <t>9BWAG45U6MT106935</t>
+  </si>
+  <si>
+    <t>291335</t>
+  </si>
+  <si>
+    <t>EM MANUTENÇÃO</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>LOCADORA</t>
-  </si>
-  <si>
-    <t>LOCADO</t>
-  </si>
-  <si>
-    <t>ALIENADO</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: GOL 1.0L MC4</t>
-  </si>
-  <si>
-    <t>CTO-1077</t>
-  </si>
-  <si>
-    <t>MOTORISTA DE APLICATIVO</t>
-  </si>
-  <si>
-    <t>LOC-1077-1/4</t>
-  </si>
-  <si>
-    <t>097.034.444-90</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>EM ANDAMENTO</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
-    <t>QGX-7353</t>
-  </si>
-  <si>
-    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t>005455-0</t>
-  </si>
-  <si>
-    <t>1149589393</t>
-  </si>
-  <si>
-    <t>9BWAG45UXJT141960</t>
-  </si>
-  <si>
-    <t>177041</t>
-  </si>
-  <si>
-    <t>2018</t>
+    <t>CTO-1006</t>
+  </si>
+  <si>
+    <t>LOC-1006-1/12</t>
+  </si>
+  <si>
+    <t>014.010.004-01</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>RGE-7H02</t>
+  </si>
+  <si>
+    <t>1253794054</t>
+  </si>
+  <si>
+    <t>9BWAG45U4MT107453</t>
+  </si>
+  <si>
+    <t>197928</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>CTO-1071</t>
+  </si>
+  <si>
+    <t>LOC-1071-1/12</t>
+  </si>
+  <si>
+    <t>009.896.264-74</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>QGT-9D76</t>
+  </si>
+  <si>
+    <t>1225842287</t>
+  </si>
+  <si>
+    <t>9BWAG45U5MT005952</t>
+  </si>
+  <si>
+    <t>208979</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>CTO-1049</t>
+  </si>
+  <si>
+    <t>LOC-1049-1/12</t>
+  </si>
+  <si>
+    <t>104.338.594-07</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>QGT-9D86</t>
+  </si>
+  <si>
+    <t>1225842635</t>
+  </si>
+  <si>
+    <t>9BWAG45U4MT005800</t>
+  </si>
+  <si>
+    <t>248065</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>CTO-1073</t>
+  </si>
+  <si>
+    <t>TERCEIRIZAÇÃO DE FROTA</t>
+  </si>
+  <si>
+    <t>LOC-1073-1/2</t>
+  </si>
+  <si>
+    <t>46.346.152/0001-41</t>
+  </si>
+  <si>
+    <t>NEW CHARGER</t>
+  </si>
+  <si>
+    <t>RGE-7H03</t>
+  </si>
+  <si>
+    <t>1253794178</t>
+  </si>
+  <si>
+    <t>9BWAG45U9MT107528</t>
+  </si>
+  <si>
+    <t>175455</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>CTO-1032</t>
+  </si>
+  <si>
+    <t>LOC-1032-1/1</t>
+  </si>
+  <si>
+    <t>122.136.017-55</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>RGE-5D71</t>
+  </si>
+  <si>
+    <t>1253120061</t>
+  </si>
+  <si>
+    <t>9BWAG45UXMT107795</t>
+  </si>
+  <si>
+    <t>224172</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>CTO-1060</t>
+  </si>
+  <si>
+    <t>LOC-1060-1/12</t>
+  </si>
+  <si>
+    <t>23.802.049/0001-63</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>QGT-1D67</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
+  </si>
+  <si>
+    <t>005493-3</t>
+  </si>
+  <si>
+    <t>1207486415</t>
+  </si>
+  <si>
+    <t>9BWDB45U7LT066973</t>
+  </si>
+  <si>
+    <t>183022</t>
+  </si>
+  <si>
+    <t>SEDAN</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/VOYAGE 1.6L MB5</t>
+  </si>
+  <si>
+    <t>CTO-1070</t>
+  </si>
+  <si>
+    <t>LOC-1070-1/12</t>
+  </si>
+  <si>
+    <t>704.631.134-03</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>QGU-1H54</t>
+  </si>
+  <si>
+    <t>1189763750</t>
+  </si>
+  <si>
+    <t>9BWDB45U5KT135660</t>
+  </si>
+  <si>
+    <t>269890</t>
+  </si>
+  <si>
+    <t>CTO-1022</t>
+  </si>
+  <si>
+    <t>LOC-1022-1/4</t>
+  </si>
+  <si>
+    <t>480.697.874-49</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>QSE-8E63</t>
+  </si>
+  <si>
+    <t>1190075218</t>
+  </si>
+  <si>
+    <t>9BWDB45U9KT124595</t>
+  </si>
+  <si>
+    <t>237305</t>
+  </si>
+  <si>
+    <t>237306</t>
+  </si>
+  <si>
+    <t>CTO-1015</t>
+  </si>
+  <si>
+    <t>LOC-1015-1/2</t>
+  </si>
+  <si>
+    <t>071.198.454-97</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>QGS-6G16</t>
+  </si>
+  <si>
+    <t>1206436686</t>
+  </si>
+  <si>
+    <t>9BWDB45U1LT065429</t>
+  </si>
+  <si>
+    <t>286361</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>CTO-1004</t>
+  </si>
+  <si>
+    <t>LOC-1004-1/5</t>
+  </si>
+  <si>
+    <t>092.354.354-63</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>QGN-9356</t>
+  </si>
+  <si>
+    <t>1164746763</t>
+  </si>
+  <si>
+    <t>9BWAG45U2KT043944</t>
+  </si>
+  <si>
+    <t>238630</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>CTO-1019</t>
+  </si>
+  <si>
+    <t>LOC-1019-1/3</t>
+  </si>
+  <si>
+    <t>017.712.914-00</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>QGS-5J76</t>
+  </si>
+  <si>
+    <t>1206038150</t>
+  </si>
+  <si>
+    <t>9BWAB45U9LT064192</t>
+  </si>
+  <si>
+    <t>153695</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/GOL 1.6L MB5</t>
+  </si>
+  <si>
+    <t>CTO-1064</t>
+  </si>
+  <si>
+    <t>LOC-1064-1/12</t>
+  </si>
+  <si>
+    <t>081.855.524-60</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>QXL-1E71</t>
+  </si>
+  <si>
+    <t>RENAULT (AUTOMÓVEIS)</t>
+  </si>
+  <si>
+    <t>SANDERO LIFE FLEX 1.0 12V 5P MEC.</t>
+  </si>
+  <si>
+    <t>025284-0</t>
+  </si>
+  <si>
+    <t>1221285065</t>
+  </si>
+  <si>
+    <t>93Y5SRZ85MJ355273</t>
+  </si>
+  <si>
+    <t>27899</t>
+  </si>
+  <si>
+    <t>PRATA</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PRÓPRIO</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: RENAULT SANDERO 10 MT</t>
+  </si>
+  <si>
+    <t>CTO-1054</t>
+  </si>
+  <si>
+    <t>LOC-1054-1/12</t>
+  </si>
+  <si>
+    <t>725.770.104-00</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>RMK-2H75</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.0 FLEX 12V 4P</t>
+  </si>
+  <si>
+    <t>005492-5</t>
+  </si>
+  <si>
+    <t>1253652063</t>
+  </si>
+  <si>
+    <t>9BWDG45U8NT005796</t>
+  </si>
+  <si>
+    <t>185202</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/VOYAGE 1.0 L MC4</t>
+  </si>
+  <si>
+    <t>CTO-1024</t>
+  </si>
+  <si>
+    <t>LOC-1024-1/7</t>
+  </si>
+  <si>
+    <t>069.054.054-00</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>EGX-2E31</t>
+  </si>
+  <si>
+    <t>1317566103</t>
+  </si>
+  <si>
+    <t>9BWAG45U9PT049067</t>
+  </si>
+  <si>
+    <t>82068</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/GOL 1.0 MPI</t>
+  </si>
+  <si>
+    <t>CTO-1038</t>
+  </si>
+  <si>
+    <t>LOC-1038-1/24</t>
+  </si>
+  <si>
+    <t>41.153.812/0001-54</t>
+  </si>
+  <si>
+    <t>SEGCOMP TECNOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>RGE-3I66</t>
+  </si>
+  <si>
+    <t>1239198733</t>
+  </si>
+  <si>
+    <t>9BWAG45U8MT050030</t>
+  </si>
+  <si>
+    <t>151003</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/GOL 1.0 L MC4</t>
+  </si>
+  <si>
+    <t>CTO-1017</t>
+  </si>
+  <si>
+    <t>LOC-1017-1/2</t>
+  </si>
+  <si>
+    <t>415.033.332-72</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>END-0I15</t>
+  </si>
+  <si>
+    <t>1329647642</t>
+  </si>
+  <si>
+    <t>9BWDG45U3PT091098</t>
+  </si>
+  <si>
+    <t>126960</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/VOYAGE MPI</t>
+  </si>
+  <si>
+    <t>CTO-1011</t>
+  </si>
+  <si>
+    <t>LOC-1011-1/9</t>
+  </si>
+  <si>
+    <t>101.093.374-41</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>RQI-7A69</t>
+  </si>
+  <si>
+    <t>HONDA (MOTOS)</t>
+  </si>
+  <si>
+    <t>CG 160 START</t>
+  </si>
+  <si>
+    <t>811139-1</t>
+  </si>
+  <si>
+    <t>1412406037</t>
+  </si>
+  <si>
+    <t>9C2KC2500RR115224</t>
+  </si>
+  <si>
+    <t>18099</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>VERMELHA</t>
+  </si>
+  <si>
+    <t>MOTO</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: HONDA/CG 160 START</t>
+  </si>
+  <si>
+    <t>LOC-1038-3/24</t>
+  </si>
+  <si>
+    <t>RQI-7A89</t>
+  </si>
+  <si>
+    <t>1412409583</t>
+  </si>
+  <si>
+    <t>9C2KC2500RR115213</t>
+  </si>
+  <si>
+    <t>14769</t>
+  </si>
+  <si>
+    <t>LOC-1038-4/24</t>
+  </si>
+  <si>
+    <t>RQJ-7H29</t>
+  </si>
+  <si>
+    <t>NXR 160 BROS ESDD FLEXONE</t>
+  </si>
+  <si>
+    <t>811130-8</t>
+  </si>
+  <si>
+    <t>1413837562</t>
+  </si>
+  <si>
+    <t>9C2KD0810RR165173</t>
+  </si>
+  <si>
+    <t>29624</t>
+  </si>
+  <si>
+    <t>PRETA</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/NOVO GOL TL MCV</t>
-  </si>
-  <si>
-    <t>CTO-1028</t>
-  </si>
-  <si>
-    <t>LOC-1028-1/8</t>
-  </si>
-  <si>
-    <t>120.205.544-37</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>RGE-5D51</t>
-  </si>
-  <si>
-    <t>1253118830</t>
-  </si>
-  <si>
-    <t>9BWAG45UXMT107456</t>
-  </si>
-  <si>
-    <t>191100</t>
-  </si>
-  <si>
-    <t>191101</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>EM MANUTENÇÃO</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/GOL 1.0L MC4</t>
-  </si>
-  <si>
-    <t>CTO-1010</t>
-  </si>
-  <si>
-    <t>LOC-1010-1/9</t>
-  </si>
-  <si>
-    <t>700.139.284-73</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>RGE-7G92</t>
-  </si>
-  <si>
-    <t>1253913371</t>
-  </si>
-  <si>
-    <t>9BWAG45U6MT106935</t>
-  </si>
-  <si>
-    <t>290950</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>CTO-1006</t>
-  </si>
-  <si>
-    <t>LOC-1006-1/12</t>
-  </si>
-  <si>
-    <t>014.010.004-01</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>RGE-7H02</t>
-  </si>
-  <si>
-    <t>1253794054</t>
-  </si>
-  <si>
-    <t>9BWAG45U4MT107453</t>
-  </si>
-  <si>
-    <t>196776</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>CTO-1071</t>
-  </si>
-  <si>
-    <t>LOC-1071-1/12</t>
-  </si>
-  <si>
-    <t>009.896.264-74</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>QGT-9D76</t>
-  </si>
-  <si>
-    <t>1225842287</t>
-  </si>
-  <si>
-    <t>9BWAG45U5MT005952</t>
-  </si>
-  <si>
-    <t>208204</t>
-  </si>
-  <si>
-    <t>208205</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>CTO-1049</t>
-  </si>
-  <si>
-    <t>LOC-1049-1/12</t>
-  </si>
-  <si>
-    <t>104.338.594-07</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>QGT-9D86</t>
-  </si>
-  <si>
-    <t>1225842635</t>
-  </si>
-  <si>
-    <t>9BWAG45U4MT005800</t>
-  </si>
-  <si>
-    <t>247746</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>CTO-1073</t>
-  </si>
-  <si>
-    <t>TERCEIRIZAÇÃO DE FROTA</t>
-  </si>
-  <si>
-    <t>LOC-1073-1/2</t>
-  </si>
-  <si>
-    <t>46.346.152/0001-41</t>
-  </si>
-  <si>
-    <t>NEW CHARGER</t>
-  </si>
-  <si>
-    <t>RGE-7H03</t>
-  </si>
-  <si>
-    <t>1253794178</t>
-  </si>
-  <si>
-    <t>9BWAG45U9MT107528</t>
-  </si>
-  <si>
-    <t>174612</t>
+    <t>VEÍCULO MIGRADO: HONDA/NXR 160 BROS</t>
+  </si>
+  <si>
+    <t>LOC-1038-2/24</t>
+  </si>
+  <si>
+    <t>FJV-6E53</t>
+  </si>
+  <si>
+    <t>1327460677</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT081265</t>
+  </si>
+  <si>
+    <t>132050</t>
+  </si>
+  <si>
+    <t>CTO-1062</t>
+  </si>
+  <si>
+    <t>LOC-1062-1/12</t>
+  </si>
+  <si>
+    <t>705.762.214-73</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>EZY-6E03</t>
+  </si>
+  <si>
+    <t>1303892356</t>
+  </si>
+  <si>
+    <t>9BWDG45U4PT034716</t>
+  </si>
+  <si>
+    <t>126410</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>CTO-1051</t>
+  </si>
+  <si>
+    <t>LOC-1051-1/12</t>
+  </si>
+  <si>
+    <t>033.444.532-97</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>ECZ-8C02</t>
+  </si>
+  <si>
+    <t>1329648010</t>
+  </si>
+  <si>
+    <t>9BWDG45U7PT091086</t>
+  </si>
+  <si>
+    <t>147001</t>
+  </si>
+  <si>
+    <t>CTO-1016</t>
+  </si>
+  <si>
+    <t>LOC-1016-1/5</t>
+  </si>
+  <si>
+    <t>117.936.764-29</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>EJZ-3D41</t>
+  </si>
+  <si>
+    <t>1327877853</t>
+  </si>
+  <si>
+    <t>9BWDG45U7PT080055</t>
+  </si>
+  <si>
+    <t>128144</t>
+  </si>
+  <si>
+    <t>CINZA</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>CTO-1047</t>
+  </si>
+  <si>
+    <t>LOC-1047-1/12</t>
+  </si>
+  <si>
+    <t>090.251.774-09</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>EVE-7G53</t>
+  </si>
+  <si>
+    <t>1319762945</t>
+  </si>
+  <si>
+    <t>9BWDG45U2PT060313</t>
+  </si>
+  <si>
+    <t>115962</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>CTO-1043</t>
+  </si>
+  <si>
+    <t>LOC-1043-1/12</t>
+  </si>
+  <si>
+    <t>704.201.114-76</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>EXF-1F14</t>
+  </si>
+  <si>
+    <t>1329889310</t>
+  </si>
+  <si>
+    <t>9BWDG45UXPT092720</t>
+  </si>
+  <si>
+    <t>119108</t>
+  </si>
+  <si>
+    <t>CTO-1029</t>
+  </si>
+  <si>
+    <t>LOC-1029-1/2</t>
+  </si>
+  <si>
+    <t>705.762.454-96</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>EWJ-2I45</t>
+  </si>
+  <si>
+    <t>1318410840</t>
+  </si>
+  <si>
+    <t>9BWDG45U0PT034373</t>
+  </si>
+  <si>
+    <t>105386</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>CTO-1056</t>
+  </si>
+  <si>
+    <t>LOC-1056-1/12</t>
+  </si>
+  <si>
+    <t>061.040.714-73</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>ECM-1C93</t>
+  </si>
+  <si>
+    <t>1325953650</t>
+  </si>
+  <si>
+    <t>9BWDG45U2PT077211</t>
+  </si>
+  <si>
+    <t>100481</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>CTO-1068</t>
+  </si>
+  <si>
+    <t>LOC-1068-1/12</t>
+  </si>
+  <si>
+    <t>086.170.784-21</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>RNC-4J20</t>
+  </si>
+  <si>
+    <t>9BWDG45U5NT045320</t>
+  </si>
+  <si>
+    <t>148000</t>
+  </si>
+  <si>
+    <t>VEÍCULO MIGRADO: VW/VOYAGE 1.0L MC4</t>
+  </si>
+  <si>
+    <t>CTO-1013</t>
+  </si>
+  <si>
+    <t>LOC-1013-1/8</t>
+  </si>
+  <si>
+    <t>966.730.874-04</t>
+  </si>
+  <si>
+    <t>MARCELO BENTO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>HDI SEGUROS S.A.</t>
+  </si>
+  <si>
+    <t>ELY-4D83</t>
+  </si>
+  <si>
+    <t>01323779938</t>
+  </si>
+  <si>
+    <t>9BWDG45U9PT071678</t>
+  </si>
+  <si>
+    <t>115331</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VEÍCULO MIGRADO: </t>
+  </si>
+  <si>
+    <t>CTO-1037</t>
+  </si>
+  <si>
+    <t>LOC-1037-1/12</t>
+  </si>
+  <si>
+    <t>077.732.684-10</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>RUC-5C24</t>
+  </si>
+  <si>
+    <t>01296669901</t>
+  </si>
+  <si>
+    <t>9BWDG45U4PT003479</t>
+  </si>
+  <si>
+    <t>102857</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>CTO-1052</t>
+  </si>
+  <si>
+    <t>CARRO POR ASSINATURA</t>
+  </si>
+  <si>
+    <t>LOC-1052-1/3</t>
+  </si>
+  <si>
+    <t>720.839.894-14</t>
+  </si>
+  <si>
+    <t>MILENA PORTILHA UGOLINI</t>
+  </si>
+  <si>
+    <t>RUC-8C45</t>
+  </si>
+  <si>
+    <t>01297099068</t>
+  </si>
+  <si>
+    <t>9BWDG45U2PT004842</t>
+  </si>
+  <si>
+    <t>126620</t>
+  </si>
+  <si>
+    <t>SÓLIDA</t>
+  </si>
+  <si>
+    <t>PENDENTE ALIENAÇÃO</t>
+  </si>
+  <si>
+    <t>CTO-1041</t>
+  </si>
+  <si>
+    <t>LOC-1041-1/12</t>
+  </si>
+  <si>
+    <t>100.144.684-41</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>EFF-7I05</t>
+  </si>
+  <si>
+    <t>01327467981</t>
+  </si>
+  <si>
+    <t>9BWDG45U5PT081673</t>
+  </si>
+  <si>
+    <t>80965</t>
   </si>
   <si>
     <t>52</t>
   </si>
   <si>
-    <t>CTO-1032</t>
-  </si>
-  <si>
-    <t>LOC-1032-1/1</t>
-  </si>
-  <si>
-    <t>122.136.017-55</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>RGE-5D71</t>
-  </si>
-  <si>
-    <t>1253120061</t>
-  </si>
-  <si>
-    <t>9BWAG45UXMT107795</t>
-  </si>
-  <si>
-    <t>223953</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>CTO-1060</t>
-  </si>
-  <si>
-    <t>LOC-1060-1/12</t>
-  </si>
-  <si>
-    <t>23.802.049/0001-63</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>QGT-1D67</t>
-  </si>
-  <si>
-    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
-  </si>
-  <si>
-    <t>005493-3</t>
-  </si>
-  <si>
-    <t>1207486415</t>
-  </si>
-  <si>
-    <t>9BWDB45U7LT066973</t>
-  </si>
-  <si>
-    <t>182607</t>
-  </si>
-  <si>
-    <t>SEDAN</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/VOYAGE 1.6L MB5</t>
-  </si>
-  <si>
-    <t>CTO-1070</t>
-  </si>
-  <si>
-    <t>LOC-1070-1/12</t>
-  </si>
-  <si>
-    <t>704.631.134-03</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>QGU-1H54</t>
-  </si>
-  <si>
-    <t>1189763750</t>
-  </si>
-  <si>
-    <t>9BWDB45U5KT135660</t>
-  </si>
-  <si>
-    <t>268414</t>
-  </si>
-  <si>
-    <t>CTO-1022</t>
-  </si>
-  <si>
-    <t>LOC-1022-1/4</t>
-  </si>
-  <si>
-    <t>480.697.874-49</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>QSE-8E63</t>
-  </si>
-  <si>
-    <t>1190075218</t>
-  </si>
-  <si>
-    <t>9BWDB45U9KT124595</t>
-  </si>
-  <si>
-    <t>236585</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>CTO-1015</t>
-  </si>
-  <si>
-    <t>LOC-1015-1/2</t>
-  </si>
-  <si>
-    <t>071.198.454-97</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>QGS-6G16</t>
-  </si>
-  <si>
-    <t>1206436686</t>
-  </si>
-  <si>
-    <t>9BWDB45U1LT065429</t>
-  </si>
-  <si>
-    <t>286228</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>CTO-1004</t>
-  </si>
-  <si>
-    <t>LOC-1004-1/5</t>
-  </si>
-  <si>
-    <t>092.354.354-63</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>QGN-9356</t>
-  </si>
-  <si>
-    <t>1164746763</t>
-  </si>
-  <si>
-    <t>9BWAG45U2KT043944</t>
-  </si>
-  <si>
-    <t>238630</t>
-  </si>
-  <si>
-    <t>CTO-1019</t>
-  </si>
-  <si>
-    <t>LOC-1019-1/3</t>
-  </si>
-  <si>
-    <t>017.712.914-00</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>QGS-5J76</t>
-  </si>
-  <si>
-    <t>1206038150</t>
-  </si>
-  <si>
-    <t>9BWAB45U9LT064192</t>
-  </si>
-  <si>
-    <t>152941</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/GOL 1.6L MB5</t>
-  </si>
-  <si>
-    <t>CTO-1064</t>
-  </si>
-  <si>
-    <t>LOC-1064-1/12</t>
-  </si>
-  <si>
-    <t>081.855.524-60</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>QXL-1E71</t>
-  </si>
-  <si>
-    <t>RENAULT (AUTOMÓVEIS)</t>
-  </si>
-  <si>
-    <t>SANDERO LIFE FLEX 1.0 12V 5P MEC.</t>
-  </si>
-  <si>
-    <t>025284-0</t>
-  </si>
-  <si>
-    <t>1221285065</t>
-  </si>
-  <si>
-    <t>93Y5SRZ85MJ355273</t>
-  </si>
-  <si>
-    <t>27383</t>
-  </si>
-  <si>
-    <t>PRATA</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>PRÓPRIO</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: RENAULT SANDERO 10 MT</t>
-  </si>
-  <si>
-    <t>CTO-1054</t>
-  </si>
-  <si>
-    <t>LOC-1054-1/12</t>
-  </si>
-  <si>
-    <t>725.770.104-00</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>RMK-2H75</t>
-  </si>
-  <si>
-    <t>VOYAGE 1.0 FLEX 12V 4P</t>
-  </si>
-  <si>
-    <t>005492-5</t>
-  </si>
-  <si>
-    <t>1253652063</t>
-  </si>
-  <si>
-    <t>9BWDG45U8NT005796</t>
-  </si>
-  <si>
-    <t>183942</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/VOYAGE 1.0 L MC4</t>
-  </si>
-  <si>
-    <t>CTO-1024</t>
-  </si>
-  <si>
-    <t>LOC-1024-1/7</t>
-  </si>
-  <si>
-    <t>069.054.054-00</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>EGX-2E31</t>
-  </si>
-  <si>
-    <t>1317566103</t>
-  </si>
-  <si>
-    <t>9BWAG45U9PT049067</t>
-  </si>
-  <si>
-    <t>81330</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/GOL 1.0 MPI</t>
-  </si>
-  <si>
-    <t>CTO-1038</t>
-  </si>
-  <si>
-    <t>LOC-1038-1/24</t>
-  </si>
-  <si>
-    <t>41.153.812/0001-54</t>
-  </si>
-  <si>
-    <t>SEGCOMP TECNOLOGIA LTDA</t>
-  </si>
-  <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>RGE-3I66</t>
-  </si>
-  <si>
-    <t>1239198733</t>
-  </si>
-  <si>
-    <t>9BWAG45U8MT050030</t>
-  </si>
-  <si>
-    <t>149982</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/GOL 1.0 L MC4</t>
-  </si>
-  <si>
-    <t>CTO-1017</t>
-  </si>
-  <si>
-    <t>LOC-1017-1/2</t>
-  </si>
-  <si>
-    <t>415.033.332-72</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>END-0I15</t>
-  </si>
-  <si>
-    <t>1329647642</t>
-  </si>
-  <si>
-    <t>9BWDG45U3PT091098</t>
-  </si>
-  <si>
-    <t>125613</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/VOYAGE MPI</t>
-  </si>
-  <si>
-    <t>CTO-1011</t>
-  </si>
-  <si>
-    <t>LOC-1011-1/9</t>
-  </si>
-  <si>
-    <t>101.093.374-41</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>RQI-7A69</t>
-  </si>
-  <si>
-    <t>HONDA (MOTOS)</t>
-  </si>
-  <si>
-    <t>CG 160 START</t>
-  </si>
-  <si>
-    <t>811139-1</t>
-  </si>
-  <si>
-    <t>1412406037</t>
-  </si>
-  <si>
-    <t>9C2KC2500RR115224</t>
-  </si>
-  <si>
-    <t>17887</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>VERMELHA</t>
-  </si>
-  <si>
-    <t>MOTO</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: HONDA/CG 160 START</t>
-  </si>
-  <si>
-    <t>LOC-1038-3/24</t>
-  </si>
-  <si>
-    <t>RQI-7A89</t>
-  </si>
-  <si>
-    <t>1412409583</t>
-  </si>
-  <si>
-    <t>9C2KC2500RR115213</t>
-  </si>
-  <si>
-    <t>14579</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>LOC-1038-4/24</t>
-  </si>
-  <si>
-    <t>RQJ-7H29</t>
-  </si>
-  <si>
-    <t>NXR 160 BROS ESDD FLEXONE</t>
-  </si>
-  <si>
-    <t>811130-8</t>
-  </si>
-  <si>
-    <t>1413837562</t>
-  </si>
-  <si>
-    <t>9C2KD0810RR165173</t>
-  </si>
-  <si>
-    <t>29554</t>
-  </si>
-  <si>
-    <t>PRETA</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: HONDA/NXR 160 BROS</t>
-  </si>
-  <si>
-    <t>LOC-1038-2/24</t>
-  </si>
-  <si>
-    <t>FJV-6E53</t>
-  </si>
-  <si>
-    <t>1327460677</t>
-  </si>
-  <si>
-    <t>9BWDG45U1PT081265</t>
-  </si>
-  <si>
-    <t>130719</t>
-  </si>
-  <si>
-    <t>CTO-1062</t>
-  </si>
-  <si>
-    <t>LOC-1062-1/12</t>
-  </si>
-  <si>
-    <t>705.762.214-73</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>EZY-6E03</t>
-  </si>
-  <si>
-    <t>1303892356</t>
-  </si>
-  <si>
-    <t>9BWDG45U4PT034716</t>
-  </si>
-  <si>
-    <t>126005</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>CTO-1051</t>
-  </si>
-  <si>
-    <t>LOC-1051-1/12</t>
-  </si>
-  <si>
-    <t>033.444.532-97</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>ECZ-8C02</t>
-  </si>
-  <si>
-    <t>1329648010</t>
-  </si>
-  <si>
-    <t>9BWDG45U7PT091086</t>
-  </si>
-  <si>
-    <t>146158</t>
-  </si>
-  <si>
-    <t>CTO-1016</t>
-  </si>
-  <si>
-    <t>LOC-1016-1/5</t>
-  </si>
-  <si>
-    <t>117.936.764-29</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>EJZ-3D41</t>
-  </si>
-  <si>
-    <t>1327877853</t>
-  </si>
-  <si>
-    <t>9BWDG45U7PT080055</t>
-  </si>
-  <si>
-    <t>127026</t>
-  </si>
-  <si>
-    <t>CINZA</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>CTO-1047</t>
-  </si>
-  <si>
-    <t>LOC-1047-1/12</t>
-  </si>
-  <si>
-    <t>090.251.774-09</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>EVE-7G53</t>
-  </si>
-  <si>
-    <t>1319762945</t>
-  </si>
-  <si>
-    <t>9BWDG45U2PT060313</t>
-  </si>
-  <si>
-    <t>114726</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>CTO-1043</t>
-  </si>
-  <si>
-    <t>LOC-1043-1/12</t>
-  </si>
-  <si>
-    <t>704.201.114-76</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>EXF-1F14</t>
-  </si>
-  <si>
-    <t>1329889310</t>
-  </si>
-  <si>
-    <t>9BWDG45UXPT092720</t>
-  </si>
-  <si>
-    <t>118033</t>
-  </si>
-  <si>
-    <t>CTO-1029</t>
-  </si>
-  <si>
-    <t>LOC-1029-1/2</t>
-  </si>
-  <si>
-    <t>705.762.454-96</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>EWJ-2I45</t>
-  </si>
-  <si>
-    <t>1318410840</t>
-  </si>
-  <si>
-    <t>9BWDG45U0PT034373</t>
-  </si>
-  <si>
-    <t>104965</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>CTO-1056</t>
-  </si>
-  <si>
-    <t>LOC-1056-1/12</t>
-  </si>
-  <si>
-    <t>061.040.714-73</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>ECM-1C93</t>
-  </si>
-  <si>
-    <t>1325953650</t>
-  </si>
-  <si>
-    <t>9BWDG45U2PT077211</t>
-  </si>
-  <si>
-    <t>99616</t>
+    <t>CTO-1063</t>
+  </si>
+  <si>
+    <t>LOC-1063-1/12</t>
+  </si>
+  <si>
+    <t>017.778.694-98</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>EMQ-6C26</t>
+  </si>
+  <si>
+    <t>01329662196</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT092539</t>
+  </si>
+  <si>
+    <t>86487</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>CTO-1018</t>
+  </si>
+  <si>
+    <t>LOC-1018-1/2</t>
+  </si>
+  <si>
+    <t>790.887.914-49</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>GIY-6G96</t>
+  </si>
+  <si>
+    <t>01298307187</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT010258</t>
+  </si>
+  <si>
+    <t>99168</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>CTO-1023</t>
+  </si>
+  <si>
+    <t>LOC-1023-1/13</t>
+  </si>
+  <si>
+    <t>009.554.944-78</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>SSW-1A28</t>
+  </si>
+  <si>
+    <t>POLO TRACK 1.0 FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>005540-9</t>
+  </si>
+  <si>
+    <t>9BWAG5R19RT023738</t>
+  </si>
+  <si>
+    <t>45764</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>CTO-1067</t>
+  </si>
+  <si>
+    <t>LOC-1067-1/12</t>
+  </si>
+  <si>
+    <t>035.542.114-35</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>STX-6G05</t>
+  </si>
+  <si>
+    <t>01387429970</t>
+  </si>
+  <si>
+    <t>9BWAG5R13RT050109</t>
+  </si>
+  <si>
+    <t>55000</t>
+  </si>
+  <si>
+    <t>2025</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>CTO-1068</t>
-  </si>
-  <si>
-    <t>LOC-1068-1/12</t>
-  </si>
-  <si>
-    <t>086.170.784-21</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>RNC-4J20</t>
-  </si>
-  <si>
-    <t>9BWDG45U5NT045320</t>
-  </si>
-  <si>
-    <t>147611</t>
-  </si>
-  <si>
-    <t>VEÍCULO MIGRADO: VW/VOYAGE 1.0L MC4</t>
-  </si>
-  <si>
-    <t>CTO-1013</t>
-  </si>
-  <si>
-    <t>LOC-1013-1/8</t>
-  </si>
-  <si>
-    <t>966.730.874-04</t>
-  </si>
-  <si>
-    <t>MARCELO BENTO DE ARAUJO</t>
-  </si>
-  <si>
-    <t>HDI SEGUROS S.A.</t>
-  </si>
-  <si>
-    <t>ELY-4D83</t>
-  </si>
-  <si>
-    <t>01323779938</t>
-  </si>
-  <si>
-    <t>9BWDG45U9PT071678</t>
-  </si>
-  <si>
-    <t>114227</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEÍCULO MIGRADO: </t>
-  </si>
-  <si>
-    <t>CTO-1037</t>
-  </si>
-  <si>
-    <t>LOC-1037-1/12</t>
-  </si>
-  <si>
-    <t>077.732.684-10</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>RUC-5C24</t>
-  </si>
-  <si>
-    <t>01296669901</t>
-  </si>
-  <si>
-    <t>9BWDG45U4PT003479</t>
-  </si>
-  <si>
-    <t>102857</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>CTO-1052</t>
-  </si>
-  <si>
-    <t>CARRO POR ASSINATURA</t>
-  </si>
-  <si>
-    <t>LOC-1052-1/3</t>
-  </si>
-  <si>
-    <t>720.839.894-14</t>
-  </si>
-  <si>
-    <t>MILENA PORTILHA UGOLINI</t>
-  </si>
-  <si>
-    <t>RUC-8C45</t>
-  </si>
-  <si>
-    <t>01297099068</t>
-  </si>
-  <si>
-    <t>9BWDG45U2PT004842</t>
-  </si>
-  <si>
-    <t>125365</t>
-  </si>
-  <si>
-    <t>SÓLIDA</t>
-  </si>
-  <si>
-    <t>PENDENTE ALIENAÇÃO</t>
-  </si>
-  <si>
-    <t>CTO-1041</t>
-  </si>
-  <si>
-    <t>LOC-1041-1/12</t>
-  </si>
-  <si>
-    <t>100.144.684-41</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>EFF-7I05</t>
-  </si>
-  <si>
-    <t>01327467981</t>
-  </si>
-  <si>
-    <t>9BWDG45U5PT081673</t>
-  </si>
-  <si>
-    <t>79855</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>CTO-1063</t>
-  </si>
-  <si>
-    <t>LOC-1063-1/12</t>
-  </si>
-  <si>
-    <t>017.778.694-98</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>EMQ-6C26</t>
-  </si>
-  <si>
-    <t>01329662196</t>
-  </si>
-  <si>
-    <t>9BWDG45U1PT092539</t>
-  </si>
-  <si>
-    <t>85491</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>CTO-1018</t>
-  </si>
-  <si>
-    <t>LOC-1018-1/2</t>
-  </si>
-  <si>
-    <t>790.887.914-49</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>GIY-6G96</t>
-  </si>
-  <si>
-    <t>01298307187</t>
-  </si>
-  <si>
-    <t>9BWDG45U1PT010258</t>
-  </si>
-  <si>
-    <t>98045</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>CTO-1023</t>
-  </si>
-  <si>
-    <t>LOC-1023-1/13</t>
-  </si>
-  <si>
-    <t>009.554.944-78</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>SSW-1A28</t>
-  </si>
-  <si>
-    <t>POLO TRACK 1.0 FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t>005540-9</t>
-  </si>
-  <si>
-    <t>9BWAG5R19RT023738</t>
-  </si>
-  <si>
-    <t>45764</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>CTO-1067</t>
-  </si>
-  <si>
-    <t>LOC-1067-1/12</t>
-  </si>
-  <si>
-    <t>035.542.114-35</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>STX-6G05</t>
-  </si>
-  <si>
-    <t>01387429970</t>
-  </si>
-  <si>
-    <t>9BWAG5R13RT050109</t>
-  </si>
-  <si>
-    <t>55000</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>CTO-1076</t>
   </si>
   <si>
@@ -1477,6 +1501,33 @@
     <t>LUZ DIVINA LTDA</t>
   </si>
   <si>
+    <t>TSW-3H91</t>
+  </si>
+  <si>
+    <t>01489397822</t>
+  </si>
+  <si>
+    <t>92VCE4CC0VK025644</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>CTO-1079</t>
+  </si>
+  <si>
+    <t>LOC-1079-1/12</t>
+  </si>
+  <si>
+    <t>068.435.674-01</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>TSW-3I03</t>
   </si>
   <si>
@@ -1498,6 +1549,27 @@
     <t>ADRIANO TEOTONIO DA SILVA</t>
   </si>
   <si>
+    <t>TSW-3I33</t>
+  </si>
+  <si>
+    <t>01489405000</t>
+  </si>
+  <si>
+    <t>92VCE4CC0VK025501</t>
+  </si>
+  <si>
+    <t>CTO-1080</t>
+  </si>
+  <si>
+    <t>LOC-1080-1/12</t>
+  </si>
+  <si>
+    <t>124.421.724-70</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
     <t>QGO-2H58</t>
   </si>
   <si>
@@ -1519,7 +1591,7 @@
     <t>2017</t>
   </si>
   <si>
-    <t>3</t>
+    <t>10</t>
   </si>
   <si>
     <t>CTO-1078</t>
@@ -1681,7 +1753,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AU52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.5564022064209" customWidth="1" style="1"/>
@@ -1919,13 +1991,13 @@
         <v>56</v>
       </c>
       <c r="I6" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K6" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="L6" s="9">
         <v>45030</v>
@@ -1976,7 +2048,7 @@
         <v>64</v>
       </c>
       <c r="AB6" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>65</v>
@@ -2038,7 +2110,7 @@
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="7">
-        <v>160016</v>
+        <v>160015</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>75</v>
@@ -2047,34 +2119,34 @@
         <v>51</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>80</v>
-      </c>
       <c r="I7" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K7" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="L7" s="9">
-        <v>45092.125</v>
+        <v>45061.125</v>
       </c>
       <c r="M7" s="10">
-        <v>45000</v>
+        <v>41500</v>
       </c>
       <c r="N7" s="10">
         <v>0</v>
@@ -2092,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="U7" s="6" t="s">
         <v>60</v>
@@ -2110,7 +2182,7 @@
         <v>62</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Z7" s="6" t="s">
         <v>57</v>
@@ -2119,22 +2191,22 @@
         <v>64</v>
       </c>
       <c r="AB7" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD7" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AE7" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF7" s="6" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="AG7" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AH7" s="6" t="s">
         <v>57</v>
@@ -2143,25 +2215,25 @@
         <v>69</v>
       </c>
       <c r="AJ7" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AK7" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AL7" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AM7" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AN7" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO7" s="9">
-        <v>45861.54583333333</v>
+        <v>46157.541666666664</v>
       </c>
       <c r="AP7" s="9">
-        <v>46174.99998842592</v>
+        <v>46237.99998842592</v>
       </c>
       <c r="AQ7" s="6" t="s">
         <v>73</v>
@@ -2176,69 +2248,69 @@
         <v>74</v>
       </c>
       <c r="AU7" s="6" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="7">
-        <v>160017</v>
+        <v>160016</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="I8" s="8">
+        <v>46160.49765046296</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="8">
+        <v>46160.49765046296</v>
+      </c>
+      <c r="L8" s="9">
+        <v>45092.125</v>
+      </c>
+      <c r="M8" s="10">
+        <v>45000</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R8" s="10">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="8">
-        <v>46149.50512731481</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K8" s="8">
-        <v>46154.50052083333</v>
-      </c>
-      <c r="L8" s="9">
-        <v>45222.125</v>
-      </c>
-      <c r="M8" s="10">
-        <v>41250</v>
-      </c>
-      <c r="N8" s="10">
-        <v>0</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R8" s="10">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="T8" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U8" s="6" t="s">
         <v>60</v>
@@ -2250,10 +2322,10 @@
         <v>61</v>
       </c>
       <c r="X8" s="6" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="Y8" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Z8" s="6" t="s">
         <v>57</v>
@@ -2262,22 +2334,22 @@
         <v>64</v>
       </c>
       <c r="AB8" s="8">
-        <v>46154.375</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AE8" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF8" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AG8" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AH8" s="6" t="s">
         <v>57</v>
@@ -2286,22 +2358,22 @@
         <v>69</v>
       </c>
       <c r="AJ8" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AK8" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AL8" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AM8" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AN8" s="6" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="AO8" s="9">
-        <v>45861.56458333333</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP8" s="9">
         <v>46174.99998842592</v>
@@ -2324,10 +2396,10 @@
     </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="7">
-        <v>160018</v>
+        <v>160017</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>51</v>
@@ -2339,25 +2411,25 @@
         <v>53</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I9" s="8">
-        <v>46153.47619212963</v>
+        <v>46163.392905092594</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K9" s="8">
-        <v>46153.47619212963</v>
+        <v>46163.392905092594</v>
       </c>
       <c r="L9" s="9">
-        <v>45105.125</v>
+        <v>45222.125</v>
       </c>
       <c r="M9" s="10">
         <v>41250</v>
@@ -2378,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="U9" s="6" t="s">
         <v>60</v>
@@ -2396,7 +2468,7 @@
         <v>62</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="Z9" s="6" t="s">
         <v>57</v>
@@ -2405,22 +2477,22 @@
         <v>64</v>
       </c>
       <c r="AB9" s="8">
-        <v>46153.47619212963</v>
+        <v>46163.392905092594</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD9" s="6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AE9" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF9" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG9" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AH9" s="6" t="s">
         <v>57</v>
@@ -2429,25 +2501,25 @@
         <v>69</v>
       </c>
       <c r="AJ9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AK9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AL9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN9" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="AK9" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AL9" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AM9" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AN9" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="AO9" s="9">
-        <v>45873.458333333336</v>
+        <v>45861.56458333333</v>
       </c>
       <c r="AP9" s="9">
-        <v>46167.99998842592</v>
+        <v>46174.99998842592</v>
       </c>
       <c r="AQ9" s="6" t="s">
         <v>73</v>
@@ -2467,10 +2539,10 @@
     </row>
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="7">
-        <v>160019</v>
+        <v>160018</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>51</v>
@@ -2482,28 +2554,28 @@
         <v>53</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="I10" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K10" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="L10" s="9">
         <v>45105.125</v>
       </c>
       <c r="M10" s="10">
-        <v>31250</v>
+        <v>41250</v>
       </c>
       <c r="N10" s="10">
         <v>0</v>
@@ -2521,10 +2593,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="U10" s="6" t="s">
         <v>60</v>
@@ -2536,10 +2608,10 @@
         <v>61</v>
       </c>
       <c r="X10" s="6" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="Y10" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Z10" s="6" t="s">
         <v>57</v>
@@ -2548,22 +2620,22 @@
         <v>64</v>
       </c>
       <c r="AB10" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="AE10" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF10" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG10" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AH10" s="6" t="s">
         <v>57</v>
@@ -2572,25 +2644,25 @@
         <v>69</v>
       </c>
       <c r="AJ10" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK10" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="AK10" s="6" t="s">
+      <c r="AL10" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="AL10" s="6" t="s">
-        <v>120</v>
-      </c>
       <c r="AM10" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AN10" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO10" s="9">
-        <v>46125.458333333336</v>
+        <v>45873.458333333336</v>
       </c>
       <c r="AP10" s="9">
-        <v>46209.99998842592</v>
+        <v>46167.99998842592</v>
       </c>
       <c r="AQ10" s="6" t="s">
         <v>73</v>
@@ -2610,10 +2682,10 @@
     </row>
     <row r="11" ht="23" customHeight="1">
       <c r="A11" s="7">
-        <v>160021</v>
+        <v>160019</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>51</v>
@@ -2625,28 +2697,28 @@
         <v>53</v>
       </c>
       <c r="F11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="I11" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K11" s="8">
-        <v>46154.495300925926</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="L11" s="9">
-        <v>45154.125</v>
+        <v>45105.125</v>
       </c>
       <c r="M11" s="10">
-        <v>41750</v>
+        <v>31250</v>
       </c>
       <c r="N11" s="10">
         <v>0</v>
@@ -2664,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>60</v>
@@ -2679,10 +2751,10 @@
         <v>61</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="Y11" s="6" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="Z11" s="6" t="s">
         <v>57</v>
@@ -2691,22 +2763,22 @@
         <v>64</v>
       </c>
       <c r="AB11" s="8">
-        <v>46154.375</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD11" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AE11" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF11" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG11" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AH11" s="6" t="s">
         <v>57</v>
@@ -2715,25 +2787,25 @@
         <v>69</v>
       </c>
       <c r="AJ11" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK11" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="AK11" s="6" t="s">
+      <c r="AL11" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="AL11" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="AM11" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AN11" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO11" s="9">
-        <v>45958.791666666664</v>
+        <v>46125.458333333336</v>
       </c>
       <c r="AP11" s="9">
-        <v>46153.99998842592</v>
+        <v>46209.99998842592</v>
       </c>
       <c r="AQ11" s="6" t="s">
         <v>73</v>
@@ -2748,15 +2820,15 @@
         <v>74</v>
       </c>
       <c r="AU11" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="7">
-        <v>160022</v>
+        <v>160021</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>51</v>
@@ -2768,28 +2840,28 @@
         <v>53</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="I12" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K12" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="L12" s="9">
-        <v>45182.125</v>
+        <v>45154.125</v>
       </c>
       <c r="M12" s="10">
-        <v>39153</v>
+        <v>41750</v>
       </c>
       <c r="N12" s="10">
         <v>0</v>
@@ -2810,7 +2882,7 @@
         <v>59</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="U12" s="6" t="s">
         <v>60</v>
@@ -2825,7 +2897,7 @@
         <v>62</v>
       </c>
       <c r="Y12" s="6" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="Z12" s="6" t="s">
         <v>57</v>
@@ -2834,49 +2906,49 @@
         <v>64</v>
       </c>
       <c r="AB12" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD12" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE12" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF12" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG12" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ12" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="AH12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI12" s="6" t="s">
+      <c r="AK12" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AJ12" s="6" t="s">
+      <c r="AL12" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="AK12" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL12" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="AM12" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AN12" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO12" s="9">
-        <v>46119.708333333336</v>
+        <v>45958.791666666664</v>
       </c>
       <c r="AP12" s="9">
-        <v>46180.708333333336</v>
+        <v>46153.99998842592</v>
       </c>
       <c r="AQ12" s="6" t="s">
         <v>73</v>
@@ -2896,10 +2968,10 @@
     </row>
     <row r="13" ht="23" customHeight="1">
       <c r="A13" s="7">
-        <v>160023</v>
+        <v>160022</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>51</v>
@@ -2911,28 +2983,28 @@
         <v>53</v>
       </c>
       <c r="F13" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>144</v>
-      </c>
       <c r="I13" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K13" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="L13" s="9">
         <v>45182.125</v>
       </c>
       <c r="M13" s="10">
-        <v>41500</v>
+        <v>39153</v>
       </c>
       <c r="N13" s="10">
         <v>0</v>
@@ -2950,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>60</v>
@@ -2968,7 +3040,7 @@
         <v>62</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="Z13" s="6" t="s">
         <v>57</v>
@@ -2977,49 +3049,49 @@
         <v>64</v>
       </c>
       <c r="AB13" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD13" s="6" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AE13" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF13" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG13" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AH13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI13" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AJ13" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="AH13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI13" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ13" s="6" t="s">
+      <c r="AK13" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="AK13" s="6" t="s">
+      <c r="AL13" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="AL13" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="AM13" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AN13" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO13" s="9">
-        <v>45861.54583333333</v>
+        <v>46119.708333333336</v>
       </c>
       <c r="AP13" s="9">
-        <v>46195.458333333336</v>
+        <v>46180.708333333336</v>
       </c>
       <c r="AQ13" s="6" t="s">
         <v>73</v>
@@ -3034,15 +3106,15 @@
         <v>74</v>
       </c>
       <c r="AU13" s="6" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
       <c r="A14" s="7">
-        <v>160024</v>
+        <v>160023</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>51</v>
@@ -3054,28 +3126,28 @@
         <v>53</v>
       </c>
       <c r="F14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="I14" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K14" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="L14" s="9">
-        <v>36526.083333333336</v>
+        <v>45182.125</v>
       </c>
       <c r="M14" s="10">
-        <v>41250</v>
+        <v>41500</v>
       </c>
       <c r="N14" s="10">
         <v>0</v>
@@ -3093,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="U14" s="6" t="s">
         <v>60</v>
@@ -3111,7 +3183,7 @@
         <v>62</v>
       </c>
       <c r="Y14" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Z14" s="6" t="s">
         <v>57</v>
@@ -3120,49 +3192,49 @@
         <v>64</v>
       </c>
       <c r="AB14" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="AE14" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF14" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG14" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AK14" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AH14" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI14" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="AJ14" s="6" t="s">
+      <c r="AL14" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="AK14" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="AL14" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="AM14" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AN14" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO14" s="9">
-        <v>46041.458333333336</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP14" s="9">
-        <v>46406.458333333336</v>
+        <v>46195.458333333336</v>
       </c>
       <c r="AQ14" s="6" t="s">
         <v>73</v>
@@ -3182,43 +3254,43 @@
     </row>
     <row r="15" ht="23" customHeight="1">
       <c r="A15" s="7">
-        <v>160026</v>
+        <v>160024</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="I15" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K15" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="L15" s="9">
-        <v>45307.125</v>
+        <v>36526.083333333336</v>
       </c>
       <c r="M15" s="10">
-        <v>42500</v>
+        <v>41250</v>
       </c>
       <c r="N15" s="10">
         <v>0</v>
@@ -3236,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>60</v>
@@ -3248,13 +3320,13 @@
         <v>57</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="X15" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>57</v>
@@ -3263,49 +3335,49 @@
         <v>64</v>
       </c>
       <c r="AB15" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD15" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AE15" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF15" s="6" t="s">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="AG15" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AH15" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AI15" s="6" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="AJ15" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AK15" s="6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AL15" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM15" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AN15" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO15" s="9">
-        <v>46118.850694444445</v>
+        <v>46041.458333333336</v>
       </c>
       <c r="AP15" s="9">
-        <v>46202.99998842592</v>
+        <v>46406.458333333336</v>
       </c>
       <c r="AQ15" s="6" t="s">
         <v>73</v>
@@ -3320,45 +3392,45 @@
         <v>74</v>
       </c>
       <c r="AU15" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
       <c r="A16" s="7">
-        <v>160027</v>
+        <v>160026</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I16" s="8">
-        <v>46153.47619212963</v>
+        <v>46161.35016203704</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K16" s="8">
-        <v>46153.47619212963</v>
+        <v>46161.35016203704</v>
       </c>
       <c r="L16" s="9">
-        <v>45308.125</v>
+        <v>45307.125</v>
       </c>
       <c r="M16" s="10">
         <v>42500</v>
@@ -3382,7 +3454,7 @@
         <v>58</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U16" s="6" t="s">
         <v>60</v>
@@ -3391,13 +3463,13 @@
         <v>57</v>
       </c>
       <c r="W16" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X16" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="Z16" s="6" t="s">
         <v>57</v>
@@ -3406,22 +3478,22 @@
         <v>64</v>
       </c>
       <c r="AB16" s="8">
-        <v>46153.47619212963</v>
+        <v>46161.35016203704</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="AE16" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF16" s="6" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="AG16" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AH16" s="6" t="s">
         <v>57</v>
@@ -3430,25 +3502,25 @@
         <v>69</v>
       </c>
       <c r="AJ16" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK16" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL16" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AM16" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN16" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO16" s="9">
-        <v>45861.54583333333</v>
+        <v>46118.850694444445</v>
       </c>
       <c r="AP16" s="9">
-        <v>46153.625</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="AQ16" s="6" t="s">
         <v>73</v>
@@ -3463,48 +3535,48 @@
         <v>74</v>
       </c>
       <c r="AU16" s="6" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
       <c r="A17" s="7">
-        <v>160028</v>
+        <v>160027</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I17" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K17" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="L17" s="9">
-        <v>45351</v>
+        <v>45308.125</v>
       </c>
       <c r="M17" s="10">
-        <v>40000</v>
+        <v>42500</v>
       </c>
       <c r="N17" s="10">
         <v>0</v>
@@ -3512,14 +3584,14 @@
       <c r="O17" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P17" s="10" t="s">
-        <v>57</v>
+      <c r="P17" s="10">
+        <v>0</v>
       </c>
       <c r="Q17" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R17" s="10" t="s">
-        <v>57</v>
+      <c r="R17" s="10">
+        <v>0</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>58</v>
@@ -3534,13 +3606,13 @@
         <v>57</v>
       </c>
       <c r="W17" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X17" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y17" s="6" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="Z17" s="6" t="s">
         <v>57</v>
@@ -3549,19 +3621,19 @@
         <v>64</v>
       </c>
       <c r="AB17" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD17" s="6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AE17" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF17" s="6" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="AG17" s="6" t="s">
         <v>186</v>
@@ -3591,7 +3663,7 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AP17" s="9">
-        <v>46167.458333333336</v>
+        <v>46209.625</v>
       </c>
       <c r="AQ17" s="6" t="s">
         <v>73</v>
@@ -3611,7 +3683,7 @@
     </row>
     <row r="18" ht="23" customHeight="1">
       <c r="A18" s="7">
-        <v>160029</v>
+        <v>160028</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>190</v>
@@ -3620,10 +3692,10 @@
         <v>51</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>191</v>
@@ -3635,19 +3707,19 @@
         <v>193</v>
       </c>
       <c r="I18" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K18" s="8">
-        <v>46153.47618055555</v>
+        <v>46163.39805555555</v>
       </c>
       <c r="L18" s="9">
-        <v>45344.125</v>
+        <v>45351</v>
       </c>
       <c r="M18" s="10">
-        <v>42000</v>
+        <v>40000</v>
       </c>
       <c r="N18" s="10">
         <v>0</v>
@@ -3655,20 +3727,20 @@
       <c r="O18" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P18" s="10">
-        <v>0</v>
+      <c r="P18" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="Q18" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R18" s="10">
-        <v>0</v>
+      <c r="R18" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>58</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>60</v>
@@ -3677,13 +3749,13 @@
         <v>57</v>
       </c>
       <c r="W18" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X18" s="6" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="Y18" s="6" t="s">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="Z18" s="6" t="s">
         <v>57</v>
@@ -3692,22 +3764,22 @@
         <v>64</v>
       </c>
       <c r="AB18" s="8">
-        <v>46153.47618055555</v>
+        <v>46163.39791666667</v>
       </c>
       <c r="AC18" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>195</v>
+        <v>93</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF18" s="6" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="AG18" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AH18" s="6" t="s">
         <v>57</v>
@@ -3716,25 +3788,25 @@
         <v>69</v>
       </c>
       <c r="AJ18" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AK18" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="AK18" s="6" t="s">
+      <c r="AL18" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="AL18" s="6" t="s">
-        <v>199</v>
-      </c>
       <c r="AM18" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN18" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO18" s="9">
-        <v>45873.458333333336</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP18" s="9">
-        <v>46188.99998842592</v>
+        <v>46167.458333333336</v>
       </c>
       <c r="AQ18" s="6" t="s">
         <v>73</v>
@@ -3754,43 +3826,43 @@
     </row>
     <row r="19" ht="23" customHeight="1">
       <c r="A19" s="7">
-        <v>160030</v>
+        <v>160029</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="F19" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>203</v>
-      </c>
       <c r="I19" s="8">
-        <v>46147.44032407407</v>
+        <v>46160.58150462963</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K19" s="8">
-        <v>46147.44032407407</v>
+        <v>46160.58150462963</v>
       </c>
       <c r="L19" s="9">
-        <v>36526.083333333336</v>
+        <v>45344.125</v>
       </c>
       <c r="M19" s="10">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="N19" s="10">
         <v>0</v>
@@ -3808,10 +3880,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>60</v>
@@ -3820,13 +3892,13 @@
         <v>57</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="X19" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y19" s="6" t="s">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="Z19" s="6" t="s">
         <v>57</v>
@@ -3835,19 +3907,19 @@
         <v>64</v>
       </c>
       <c r="AB19" s="8">
-        <v>46147.44032407407</v>
+        <v>46160.58150462963</v>
       </c>
       <c r="AC19" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD19" s="6" t="s">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="AE19" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF19" s="6" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="AG19" s="6" t="s">
         <v>204</v>
@@ -3874,10 +3946,10 @@
         <v>57</v>
       </c>
       <c r="AO19" s="9">
-        <v>45861.54583333333</v>
+        <v>45873.458333333336</v>
       </c>
       <c r="AP19" s="9">
-        <v>46195.458333333336</v>
+        <v>46188.99998842592</v>
       </c>
       <c r="AQ19" s="6" t="s">
         <v>73</v>
@@ -3897,7 +3969,7 @@
     </row>
     <row r="20" ht="23" customHeight="1">
       <c r="A20" s="7">
-        <v>160031</v>
+        <v>160030</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>208</v>
@@ -3921,19 +3993,19 @@
         <v>211</v>
       </c>
       <c r="I20" s="8">
-        <v>46154.48504629629</v>
+        <v>46147.44032407407</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>211</v>
       </c>
       <c r="K20" s="8">
-        <v>46154.48504629629</v>
+        <v>46147.44032407407</v>
       </c>
       <c r="L20" s="9">
-        <v>45364.125</v>
+        <v>36526.083333333336</v>
       </c>
       <c r="M20" s="10">
-        <v>41056.97</v>
+        <v>39000</v>
       </c>
       <c r="N20" s="10">
         <v>0</v>
@@ -3951,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="T20" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="T20" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="U20" s="6" t="s">
         <v>60</v>
@@ -3969,7 +4041,7 @@
         <v>62</v>
       </c>
       <c r="Y20" s="6" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="Z20" s="6" t="s">
         <v>57</v>
@@ -3978,22 +4050,22 @@
         <v>64</v>
       </c>
       <c r="AB20" s="8">
-        <v>46154.48504629629</v>
+        <v>46147.44032407407</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD20" s="6" t="s">
-        <v>212</v>
+        <v>93</v>
       </c>
       <c r="AE20" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF20" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG20" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="AG20" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="AH20" s="6" t="s">
         <v>57</v>
@@ -4002,25 +4074,25 @@
         <v>69</v>
       </c>
       <c r="AJ20" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK20" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="AK20" s="6" t="s">
+      <c r="AL20" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AL20" s="6" t="s">
-        <v>217</v>
-      </c>
       <c r="AM20" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AN20" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO20" s="9">
-        <v>46092.708333333336</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP20" s="9">
-        <v>46174.99998842592</v>
+        <v>46195.458333333336</v>
       </c>
       <c r="AQ20" s="6" t="s">
         <v>73</v>
@@ -4035,48 +4107,48 @@
         <v>74</v>
       </c>
       <c r="AU20" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
       <c r="A21" s="7">
-        <v>160032</v>
+        <v>160031</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>224</v>
-      </c>
       <c r="I21" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="K21" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="L21" s="9">
-        <v>36526.083333333336</v>
+        <v>45364.125</v>
       </c>
       <c r="M21" s="10">
-        <v>1</v>
+        <v>41056.97</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
@@ -4094,13 +4166,13 @@
         <v>0</v>
       </c>
       <c r="S21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="T21" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T21" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="U21" s="6" t="s">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="V21" s="6" t="s">
         <v>57</v>
@@ -4112,7 +4184,7 @@
         <v>62</v>
       </c>
       <c r="Y21" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="Z21" s="6" t="s">
         <v>57</v>
@@ -4121,22 +4193,22 @@
         <v>64</v>
       </c>
       <c r="AB21" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD21" s="6" t="s">
-        <v>155</v>
+        <v>222</v>
       </c>
       <c r="AE21" s="6" t="s">
-        <v>227</v>
+        <v>66</v>
       </c>
       <c r="AF21" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AG21" s="6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AH21" s="6" t="s">
         <v>57</v>
@@ -4145,25 +4217,25 @@
         <v>69</v>
       </c>
       <c r="AJ21" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AK21" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AL21" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AM21" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AN21" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO21" s="9">
-        <v>46003.645833333336</v>
+        <v>46092.708333333336</v>
       </c>
       <c r="AP21" s="9">
-        <v>46139.99998842592</v>
+        <v>46174.99998842592</v>
       </c>
       <c r="AQ21" s="6" t="s">
         <v>73</v>
@@ -4183,79 +4255,79 @@
     </row>
     <row r="22" ht="23" customHeight="1">
       <c r="A22" s="7">
-        <v>160033</v>
+        <v>160032</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="I22" s="8">
+        <v>46160.49765046296</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="K22" s="8">
+        <v>46160.49765046296</v>
+      </c>
+      <c r="L22" s="9">
+        <v>36526.083333333336</v>
+      </c>
+      <c r="M22" s="10">
+        <v>1</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R22" s="10">
+        <v>0</v>
+      </c>
+      <c r="S22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="T22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="U22" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="V22" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="W22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="X22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y22" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="I22" s="8">
-        <v>46153.47620370371</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="K22" s="8">
-        <v>46153.47620370371</v>
-      </c>
-      <c r="L22" s="9">
-        <v>45475.125</v>
-      </c>
-      <c r="M22" s="10">
-        <v>45500</v>
-      </c>
-      <c r="N22" s="10">
-        <v>0</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R22" s="10">
-        <v>0</v>
-      </c>
-      <c r="S22" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="T22" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="U22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="V22" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="W22" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="X22" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y22" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="Z22" s="6" t="s">
         <v>57</v>
@@ -4264,22 +4336,22 @@
         <v>64</v>
       </c>
       <c r="AB22" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD22" s="6" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="AE22" s="6" t="s">
-        <v>66</v>
+        <v>237</v>
       </c>
       <c r="AF22" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG22" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AH22" s="6" t="s">
         <v>57</v>
@@ -4288,25 +4360,25 @@
         <v>69</v>
       </c>
       <c r="AJ22" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK22" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="AL22" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="AK22" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="AL22" s="6" t="s">
-        <v>244</v>
-      </c>
       <c r="AM22" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AN22" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO22" s="9">
-        <v>45861.54583333333</v>
+        <v>46003.645833333336</v>
       </c>
       <c r="AP22" s="9">
-        <v>46167.99998842592</v>
+        <v>46139.99998842592</v>
       </c>
       <c r="AQ22" s="6" t="s">
         <v>73</v>
@@ -4321,24 +4393,24 @@
         <v>74</v>
       </c>
       <c r="AU22" s="6" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
       <c r="A23" s="7">
-        <v>160034</v>
+        <v>160033</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>53</v>
+        <v>245</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>246</v>
@@ -4350,19 +4422,19 @@
         <v>248</v>
       </c>
       <c r="I23" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>248</v>
       </c>
       <c r="K23" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="L23" s="9">
-        <v>36526.083333333336</v>
+        <v>45475.125</v>
       </c>
       <c r="M23" s="10">
-        <v>46800</v>
+        <v>45500</v>
       </c>
       <c r="N23" s="10">
         <v>0</v>
@@ -4380,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>239</v>
+        <v>103</v>
       </c>
       <c r="T23" s="6" t="s">
         <v>249</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="V23" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W23" s="6" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="X23" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y23" s="6" t="s">
-        <v>250</v>
+        <v>124</v>
       </c>
       <c r="Z23" s="6" t="s">
         <v>57</v>
@@ -4407,49 +4479,49 @@
         <v>64</v>
       </c>
       <c r="AB23" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD23" s="6" t="s">
-        <v>251</v>
+        <v>93</v>
       </c>
       <c r="AE23" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF23" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="AG23" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AH23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ23" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="AG23" s="6" t="s">
+      <c r="AK23" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="AH23" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI23" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="AJ23" s="6" t="s">
+      <c r="AL23" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="AK23" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="AL23" s="6" t="s">
-        <v>256</v>
-      </c>
       <c r="AM23" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AN23" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO23" s="9">
-        <v>45590.458333333336</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP23" s="9">
-        <v>46320.458333333336</v>
+        <v>46167.99998842592</v>
       </c>
       <c r="AQ23" s="6" t="s">
         <v>73</v>
@@ -4464,15 +4536,15 @@
         <v>74</v>
       </c>
       <c r="AU23" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
       <c r="A24" s="7">
-        <v>160035</v>
+        <v>160034</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>51</v>
@@ -4484,52 +4556,52 @@
         <v>53</v>
       </c>
       <c r="F24" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="I24" s="8">
+        <v>46160.49762731481</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="K24" s="8">
+        <v>46160.49762731481</v>
+      </c>
+      <c r="L24" s="9">
+        <v>36526.083333333336</v>
+      </c>
+      <c r="M24" s="10">
+        <v>46800</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P24" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R24" s="10">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="T24" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="I24" s="8">
-        <v>46153.47619212963</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="K24" s="8">
-        <v>46153.47619212963</v>
-      </c>
-      <c r="L24" s="9">
-        <v>45539.125</v>
-      </c>
-      <c r="M24" s="10">
-        <v>43500</v>
-      </c>
-      <c r="N24" s="10">
-        <v>0</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P24" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R24" s="10">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="T24" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="U24" s="6" t="s">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="V24" s="6" t="s">
         <v>57</v>
@@ -4541,7 +4613,7 @@
         <v>62</v>
       </c>
       <c r="Y24" s="6" t="s">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="Z24" s="6" t="s">
         <v>57</v>
@@ -4550,13 +4622,13 @@
         <v>64</v>
       </c>
       <c r="AB24" s="8">
-        <v>46153.47619212963</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD24" s="6" t="s">
-        <v>83</v>
+        <v>261</v>
       </c>
       <c r="AE24" s="6" t="s">
         <v>66</v>
@@ -4571,7 +4643,7 @@
         <v>57</v>
       </c>
       <c r="AI24" s="6" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="AJ24" s="6" t="s">
         <v>264</v>
@@ -4583,16 +4655,16 @@
         <v>266</v>
       </c>
       <c r="AM24" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN24" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO24" s="9">
-        <v>45861.54583333333</v>
+        <v>45590.458333333336</v>
       </c>
       <c r="AP24" s="9">
-        <v>46167.458333333336</v>
+        <v>46320.458333333336</v>
       </c>
       <c r="AQ24" s="6" t="s">
         <v>73</v>
@@ -4607,48 +4679,48 @@
         <v>74</v>
       </c>
       <c r="AU24" s="6" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
       <c r="A25" s="7">
-        <v>160036</v>
+        <v>160035</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>234</v>
+        <v>52</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>235</v>
+        <v>53</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I25" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K25" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="L25" s="9">
-        <v>36526.083333333336</v>
+        <v>45539.125</v>
       </c>
       <c r="M25" s="10">
-        <v>49900</v>
+        <v>43500</v>
       </c>
       <c r="N25" s="10">
         <v>0</v>
@@ -4666,10 +4738,10 @@
         <v>0</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>60</v>
@@ -4678,13 +4750,13 @@
         <v>57</v>
       </c>
       <c r="W25" s="6" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="X25" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y25" s="6" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="Z25" s="6" t="s">
         <v>57</v>
@@ -4693,22 +4765,22 @@
         <v>64</v>
       </c>
       <c r="AB25" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49765046296</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD25" s="6" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="AE25" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF25" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG25" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AH25" s="6" t="s">
         <v>57</v>
@@ -4717,25 +4789,25 @@
         <v>69</v>
       </c>
       <c r="AJ25" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AK25" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL25" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM25" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN25" s="6" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="AO25" s="9">
         <v>45861.54583333333</v>
       </c>
       <c r="AP25" s="9">
-        <v>46174.99998842592</v>
+        <v>46167.458333333336</v>
       </c>
       <c r="AQ25" s="6" t="s">
         <v>73</v>
@@ -4755,43 +4827,43 @@
     </row>
     <row r="26" ht="23" customHeight="1">
       <c r="A26" s="7">
-        <v>160037</v>
+        <v>160036</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>277</v>
+        <v>51</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="I26" s="8">
-        <v>46154.49039351852</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K26" s="8">
-        <v>46154.49039351852</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="L26" s="9">
         <v>36526.083333333336</v>
       </c>
       <c r="M26" s="10">
-        <v>18629</v>
+        <v>49900</v>
       </c>
       <c r="N26" s="10">
         <v>0</v>
@@ -4809,25 +4881,25 @@
         <v>0</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>284</v>
+        <v>60</v>
       </c>
       <c r="V26" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W26" s="6" t="s">
-        <v>285</v>
+        <v>174</v>
       </c>
       <c r="X26" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y26" s="6" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="Z26" s="6" t="s">
         <v>57</v>
@@ -4836,49 +4908,49 @@
         <v>64</v>
       </c>
       <c r="AB26" s="8">
-        <v>46154.49039351852</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD26" s="6" t="s">
-        <v>251</v>
+        <v>163</v>
       </c>
       <c r="AE26" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF26" s="6" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AG26" s="6" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="AH26" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AI26" s="6" t="s">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="AJ26" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AK26" s="6" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="AL26" s="6" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="AM26" s="6" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="AN26" s="6" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="AO26" s="9">
-        <v>45590.458333333336</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP26" s="9">
-        <v>46320.458333333336</v>
+        <v>46174.99998842592</v>
       </c>
       <c r="AQ26" s="6" t="s">
         <v>73</v>
@@ -4893,42 +4965,42 @@
         <v>74</v>
       </c>
       <c r="AU26" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
       <c r="A27" s="7">
-        <v>160038</v>
+        <v>160037</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>278</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I27" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K27" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="L27" s="9">
         <v>36526.083333333336</v>
@@ -4952,25 +5024,25 @@
         <v>0</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="U27" s="6" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="V27" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W27" s="6" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="X27" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y27" s="6" t="s">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="Z27" s="6" t="s">
         <v>57</v>
@@ -4979,40 +5051,40 @@
         <v>64</v>
       </c>
       <c r="AB27" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD27" s="6" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AE27" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF27" s="6" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AG27" s="6" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="AH27" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AI27" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AJ27" s="6" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AK27" s="6" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AL27" s="6" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AM27" s="6" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="AN27" s="6" t="s">
         <v>57</v>
@@ -5041,43 +5113,43 @@
     </row>
     <row r="28" ht="23" customHeight="1">
       <c r="A28" s="7">
-        <v>160039</v>
+        <v>160038</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I28" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K28" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="L28" s="9">
         <v>36526.083333333336</v>
       </c>
       <c r="M28" s="10">
-        <v>7899</v>
+        <v>18629</v>
       </c>
       <c r="N28" s="10">
         <v>0</v>
@@ -5095,25 +5167,25 @@
         <v>0</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="V28" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W28" s="6" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="X28" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y28" s="6" t="s">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="Z28" s="6" t="s">
         <v>57</v>
@@ -5122,40 +5194,40 @@
         <v>64</v>
       </c>
       <c r="AB28" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD28" s="6" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AE28" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF28" s="6" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AG28" s="6" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="AH28" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AI28" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AJ28" s="6" t="s">
         <v>302</v>
       </c>
       <c r="AK28" s="6" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AL28" s="6" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AM28" s="6" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="AN28" s="6" t="s">
         <v>57</v>
@@ -5184,43 +5256,43 @@
     </row>
     <row r="29" ht="23" customHeight="1">
       <c r="A29" s="7">
-        <v>160040</v>
+        <v>160039</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>303</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>51</v>
+        <v>287</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>235</v>
+        <v>305</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I29" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K29" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="L29" s="9">
-        <v>45934.125</v>
+        <v>36526.083333333336</v>
       </c>
       <c r="M29" s="10">
-        <v>50900</v>
+        <v>7899</v>
       </c>
       <c r="N29" s="10">
         <v>0</v>
@@ -5238,25 +5310,25 @@
         <v>0</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>60</v>
+        <v>309</v>
       </c>
       <c r="V29" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W29" s="6" t="s">
-        <v>166</v>
+        <v>295</v>
       </c>
       <c r="X29" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y29" s="6" t="s">
-        <v>145</v>
+        <v>310</v>
       </c>
       <c r="Z29" s="6" t="s">
         <v>57</v>
@@ -5265,49 +5337,49 @@
         <v>64</v>
       </c>
       <c r="AB29" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD29" s="6" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="AE29" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF29" s="6" t="s">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="AG29" s="6" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="AH29" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AI29" s="6" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="AJ29" s="6" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AK29" s="6" t="s">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="AL29" s="6" t="s">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="AM29" s="6" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="AN29" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO29" s="9">
-        <v>46056.833333333336</v>
+        <v>45590.458333333336</v>
       </c>
       <c r="AP29" s="9">
-        <v>46139.99998842592</v>
+        <v>46320.458333333336</v>
       </c>
       <c r="AQ29" s="6" t="s">
         <v>73</v>
@@ -5327,43 +5399,43 @@
     </row>
     <row r="30" ht="23" customHeight="1">
       <c r="A30" s="7">
-        <v>160041</v>
+        <v>160040</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I30" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K30" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="L30" s="9">
-        <v>45575</v>
+        <v>45934.125</v>
       </c>
       <c r="M30" s="10">
-        <v>46450</v>
+        <v>50900</v>
       </c>
       <c r="N30" s="10">
         <v>0</v>
@@ -5371,20 +5443,20 @@
       <c r="O30" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P30" s="10" t="s">
-        <v>57</v>
+      <c r="P30" s="10">
+        <v>0</v>
       </c>
       <c r="Q30" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R30" s="10" t="s">
-        <v>57</v>
+      <c r="R30" s="10">
+        <v>0</v>
       </c>
       <c r="S30" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U30" s="6" t="s">
         <v>60</v>
@@ -5393,13 +5465,13 @@
         <v>57</v>
       </c>
       <c r="W30" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X30" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y30" s="6" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="Z30" s="6" t="s">
         <v>57</v>
@@ -5408,22 +5480,22 @@
         <v>64</v>
       </c>
       <c r="AB30" s="8">
-        <v>46153.47618055555</v>
+        <v>46160.49763888889</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD30" s="6" t="s">
-        <v>315</v>
+        <v>163</v>
       </c>
       <c r="AE30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF30" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AG30" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AH30" s="6" t="s">
         <v>57</v>
@@ -5432,25 +5504,25 @@
         <v>69</v>
       </c>
       <c r="AJ30" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AK30" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL30" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM30" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN30" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO30" s="9">
-        <v>45980.666666666664</v>
+        <v>46056.833333333336</v>
       </c>
       <c r="AP30" s="9">
-        <v>46174.99998842592</v>
+        <v>46139.99998842592</v>
       </c>
       <c r="AQ30" s="6" t="s">
         <v>73</v>
@@ -5470,43 +5542,43 @@
     </row>
     <row r="31" ht="23" customHeight="1">
       <c r="A31" s="7">
-        <v>160042</v>
+        <v>160041</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I31" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K31" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="L31" s="9">
-        <v>36526</v>
+        <v>45575</v>
       </c>
       <c r="M31" s="10">
-        <v>1</v>
+        <v>46450</v>
       </c>
       <c r="N31" s="10">
         <v>0</v>
@@ -5524,10 +5596,10 @@
         <v>57</v>
       </c>
       <c r="S31" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T31" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U31" s="6" t="s">
         <v>60</v>
@@ -5536,13 +5608,13 @@
         <v>57</v>
       </c>
       <c r="W31" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X31" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y31" s="6" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="Z31" s="6" t="s">
         <v>57</v>
@@ -5551,22 +5623,22 @@
         <v>64</v>
       </c>
       <c r="AB31" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD31" s="6" t="s">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AE31" s="6" t="s">
-        <v>227</v>
+        <v>66</v>
       </c>
       <c r="AF31" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AG31" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AH31" s="6" t="s">
         <v>57</v>
@@ -5575,22 +5647,22 @@
         <v>69</v>
       </c>
       <c r="AJ31" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AK31" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL31" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AM31" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN31" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO31" s="9">
-        <v>45861.54583333333</v>
+        <v>45980.666666666664</v>
       </c>
       <c r="AP31" s="9">
         <v>46174.99998842592</v>
@@ -5608,48 +5680,48 @@
         <v>74</v>
       </c>
       <c r="AU31" s="6" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
       <c r="A32" s="7">
-        <v>160043</v>
+        <v>160042</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I32" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497615740744</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K32" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497615740744</v>
       </c>
       <c r="L32" s="9">
-        <v>36526.083333333336</v>
+        <v>36526</v>
       </c>
       <c r="M32" s="10">
-        <v>49400</v>
+        <v>1</v>
       </c>
       <c r="N32" s="10">
         <v>0</v>
@@ -5657,35 +5729,35 @@
       <c r="O32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P32" s="10">
-        <v>0</v>
+      <c r="P32" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="Q32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R32" s="10">
-        <v>0</v>
+      <c r="R32" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="S32" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T32" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U32" s="6" t="s">
-        <v>332</v>
+        <v>60</v>
       </c>
       <c r="V32" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W32" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X32" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y32" s="6" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="Z32" s="6" t="s">
         <v>57</v>
@@ -5694,19 +5766,19 @@
         <v>64</v>
       </c>
       <c r="AB32" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497615740744</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD32" s="6" t="s">
-        <v>333</v>
+        <v>93</v>
       </c>
       <c r="AE32" s="6" t="s">
-        <v>66</v>
+        <v>237</v>
       </c>
       <c r="AF32" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AG32" s="6" t="s">
         <v>334</v>
@@ -5733,10 +5805,10 @@
         <v>57</v>
       </c>
       <c r="AO32" s="9">
-        <v>45957.458333333336</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP32" s="9">
-        <v>46153.99998842592</v>
+        <v>46174.99998842592</v>
       </c>
       <c r="AQ32" s="6" t="s">
         <v>73</v>
@@ -5751,12 +5823,12 @@
         <v>74</v>
       </c>
       <c r="AU32" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
       <c r="A33" s="7">
-        <v>160044</v>
+        <v>160043</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>338</v>
@@ -5765,10 +5837,10 @@
         <v>51</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>339</v>
@@ -5780,13 +5852,13 @@
         <v>341</v>
       </c>
       <c r="I33" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>341</v>
       </c>
       <c r="K33" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="L33" s="9">
         <v>36526.083333333336</v>
@@ -5810,25 +5882,25 @@
         <v>0</v>
       </c>
       <c r="S33" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T33" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U33" s="6" t="s">
-        <v>225</v>
+        <v>342</v>
       </c>
       <c r="V33" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W33" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X33" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y33" s="6" t="s">
-        <v>342</v>
+        <v>236</v>
       </c>
       <c r="Z33" s="6" t="s">
         <v>57</v>
@@ -5837,7 +5909,7 @@
         <v>64</v>
       </c>
       <c r="AB33" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>65</v>
@@ -5849,7 +5921,7 @@
         <v>66</v>
       </c>
       <c r="AF33" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AG33" s="6" t="s">
         <v>344</v>
@@ -5876,10 +5948,10 @@
         <v>57</v>
       </c>
       <c r="AO33" s="9">
-        <v>45915.458333333336</v>
+        <v>45957.458333333336</v>
       </c>
       <c r="AP33" s="9">
-        <v>46139.99998842592</v>
+        <v>46153.99998842592</v>
       </c>
       <c r="AQ33" s="6" t="s">
         <v>73</v>
@@ -5899,7 +5971,7 @@
     </row>
     <row r="34" ht="23" customHeight="1">
       <c r="A34" s="7">
-        <v>160045</v>
+        <v>160044</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>348</v>
@@ -5908,10 +5980,10 @@
         <v>51</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>349</v>
@@ -5923,19 +5995,19 @@
         <v>351</v>
       </c>
       <c r="I34" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>351</v>
       </c>
       <c r="K34" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="L34" s="9">
-        <v>45729</v>
+        <v>36526.083333333336</v>
       </c>
       <c r="M34" s="10">
-        <v>44505</v>
+        <v>49400</v>
       </c>
       <c r="N34" s="10">
         <v>0</v>
@@ -5943,35 +6015,35 @@
       <c r="O34" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P34" s="10" t="s">
-        <v>57</v>
+      <c r="P34" s="10">
+        <v>0</v>
       </c>
       <c r="Q34" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R34" s="10" t="s">
-        <v>57</v>
+      <c r="R34" s="10">
+        <v>0</v>
       </c>
       <c r="S34" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T34" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="V34" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X34" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y34" s="6" t="s">
-        <v>250</v>
+        <v>352</v>
       </c>
       <c r="Z34" s="6" t="s">
         <v>57</v>
@@ -5980,22 +6052,22 @@
         <v>64</v>
       </c>
       <c r="AB34" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD34" s="6" t="s">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AE34" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF34" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AG34" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AH34" s="6" t="s">
         <v>57</v>
@@ -6004,25 +6076,25 @@
         <v>69</v>
       </c>
       <c r="AJ34" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AK34" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AL34" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AM34" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AN34" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO34" s="9">
-        <v>45861.54583333333</v>
+        <v>45915.458333333336</v>
       </c>
       <c r="AP34" s="9">
-        <v>46139.458333333336</v>
+        <v>46139.99998842592</v>
       </c>
       <c r="AQ34" s="6" t="s">
         <v>73</v>
@@ -6031,54 +6103,54 @@
         <v>57</v>
       </c>
       <c r="AS34" s="6" t="s">
-        <v>356</v>
+        <v>74</v>
       </c>
       <c r="AT34" s="6" t="s">
         <v>74</v>
       </c>
       <c r="AU34" s="6" t="s">
-        <v>356</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
       <c r="A35" s="7">
-        <v>160046</v>
+        <v>160045</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I35" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K35" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="L35" s="9">
-        <v>45736</v>
+        <v>45729</v>
       </c>
       <c r="M35" s="10">
-        <v>51300</v>
+        <v>44505</v>
       </c>
       <c r="N35" s="10">
         <v>0</v>
@@ -6096,10 +6168,10 @@
         <v>57</v>
       </c>
       <c r="S35" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T35" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U35" s="6" t="s">
         <v>60</v>
@@ -6108,13 +6180,13 @@
         <v>57</v>
       </c>
       <c r="W35" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X35" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y35" s="6" t="s">
-        <v>361</v>
+        <v>260</v>
       </c>
       <c r="Z35" s="6" t="s">
         <v>57</v>
@@ -6123,22 +6195,22 @@
         <v>64</v>
       </c>
       <c r="AB35" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC35" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD35" s="6" t="s">
-        <v>362</v>
+        <v>93</v>
       </c>
       <c r="AE35" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF35" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AG35" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AH35" s="6" t="s">
         <v>57</v>
@@ -6147,25 +6219,25 @@
         <v>69</v>
       </c>
       <c r="AJ35" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="AK35" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="AK35" s="6" t="s">
+      <c r="AL35" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="AL35" s="6" t="s">
-        <v>366</v>
-      </c>
       <c r="AM35" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AN35" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO35" s="9">
-        <v>46031.791666666664</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP35" s="9">
-        <v>46195.99998842592</v>
+        <v>46139.458333333336</v>
       </c>
       <c r="AQ35" s="6" t="s">
         <v>73</v>
@@ -6174,18 +6246,18 @@
         <v>57</v>
       </c>
       <c r="AS35" s="6" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AT35" s="6" t="s">
         <v>74</v>
       </c>
       <c r="AU35" s="6" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
       <c r="A36" s="7">
-        <v>160047</v>
+        <v>160046</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>367</v>
@@ -6194,10 +6266,10 @@
         <v>51</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>368</v>
@@ -6209,19 +6281,19 @@
         <v>370</v>
       </c>
       <c r="I36" s="8">
-        <v>46153.47615740741</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>370</v>
       </c>
       <c r="K36" s="8">
-        <v>46153.47615740741</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="L36" s="9">
-        <v>45739.125</v>
+        <v>45736</v>
       </c>
       <c r="M36" s="10">
-        <v>53000</v>
+        <v>51300</v>
       </c>
       <c r="N36" s="10">
         <v>0</v>
@@ -6229,20 +6301,20 @@
       <c r="O36" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P36" s="10">
-        <v>0</v>
+      <c r="P36" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="Q36" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R36" s="10">
-        <v>0</v>
+      <c r="R36" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="S36" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T36" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U36" s="6" t="s">
         <v>60</v>
@@ -6251,7 +6323,7 @@
         <v>57</v>
       </c>
       <c r="W36" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X36" s="6" t="s">
         <v>62</v>
@@ -6266,7 +6338,7 @@
         <v>64</v>
       </c>
       <c r="AB36" s="8">
-        <v>46153.47615740741</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC36" s="6" t="s">
         <v>65</v>
@@ -6278,7 +6350,7 @@
         <v>66</v>
       </c>
       <c r="AF36" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AG36" s="6" t="s">
         <v>373</v>
@@ -6305,10 +6377,10 @@
         <v>57</v>
       </c>
       <c r="AO36" s="9">
-        <v>46097.805555555555</v>
+        <v>46031.791666666664</v>
       </c>
       <c r="AP36" s="9">
-        <v>46181.99998842592</v>
+        <v>46195.99998842592</v>
       </c>
       <c r="AQ36" s="6" t="s">
         <v>73</v>
@@ -6317,18 +6389,18 @@
         <v>57</v>
       </c>
       <c r="AS36" s="6" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AT36" s="6" t="s">
         <v>74</v>
       </c>
       <c r="AU36" s="6" t="s">
-        <v>57</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
       <c r="A37" s="7">
-        <v>160049</v>
+        <v>160047</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>377</v>
@@ -6337,34 +6409,34 @@
         <v>51</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>57</v>
+        <v>378</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I37" s="8">
-        <v>46154.482766203706</v>
+        <v>46160.497615740744</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K37" s="8">
-        <v>46154.482766203706</v>
+        <v>46160.497615740744</v>
       </c>
       <c r="L37" s="9">
-        <v>45833</v>
+        <v>45739.125</v>
       </c>
       <c r="M37" s="10">
-        <v>49600</v>
+        <v>53000</v>
       </c>
       <c r="N37" s="10">
         <v>0</v>
@@ -6372,35 +6444,35 @@
       <c r="O37" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P37" s="10" t="s">
-        <v>57</v>
+      <c r="P37" s="10">
+        <v>0</v>
       </c>
       <c r="Q37" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R37" s="10" t="s">
-        <v>57</v>
+      <c r="R37" s="10">
+        <v>0</v>
       </c>
       <c r="S37" s="6" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="T37" s="6" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="U37" s="6" t="s">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="V37" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W37" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X37" s="6" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="Y37" s="6" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="Z37" s="6" t="s">
         <v>57</v>
@@ -6409,22 +6481,22 @@
         <v>64</v>
       </c>
       <c r="AB37" s="8">
-        <v>46154.482766203706</v>
+        <v>46160.497615740744</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD37" s="6" t="s">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="AE37" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF37" s="6" t="s">
-        <v>380</v>
+        <v>281</v>
       </c>
       <c r="AG37" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AH37" s="6" t="s">
         <v>57</v>
@@ -6433,45 +6505,45 @@
         <v>69</v>
       </c>
       <c r="AJ37" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AK37" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL37" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM37" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN37" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO37" s="9">
-        <v>45861.54583333333</v>
+        <v>46097.805555555555</v>
       </c>
       <c r="AP37" s="9">
-        <v>46174.99998842592</v>
+        <v>46181.99998842592</v>
       </c>
       <c r="AQ37" s="6" t="s">
         <v>73</v>
       </c>
       <c r="AR37" s="6" t="s">
-        <v>385</v>
+        <v>57</v>
       </c>
       <c r="AS37" s="6" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AT37" s="6" t="s">
         <v>74</v>
       </c>
       <c r="AU37" s="6" t="s">
-        <v>356</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
       <c r="A38" s="7">
-        <v>160050</v>
+        <v>160049</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>386</v>
@@ -6480,34 +6552,34 @@
         <v>51</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F38" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>389</v>
-      </c>
       <c r="I38" s="8">
-        <v>46153.476168981484</v>
+        <v>46163.43991898148</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K38" s="8">
-        <v>46153.476168981484</v>
+        <v>46163.43991898148</v>
       </c>
       <c r="L38" s="9">
-        <v>45832.125</v>
+        <v>45833</v>
       </c>
       <c r="M38" s="10">
-        <v>52700</v>
+        <v>49600</v>
       </c>
       <c r="N38" s="10">
         <v>0</v>
@@ -6515,35 +6587,35 @@
       <c r="O38" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P38" s="10">
-        <v>0</v>
+      <c r="P38" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="Q38" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R38" s="10">
-        <v>0</v>
+      <c r="R38" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>239</v>
+        <v>103</v>
       </c>
       <c r="T38" s="6" t="s">
         <v>249</v>
       </c>
       <c r="U38" s="6" t="s">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="V38" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W38" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X38" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y38" s="6" t="s">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="Z38" s="6" t="s">
         <v>57</v>
@@ -6552,22 +6624,22 @@
         <v>64</v>
       </c>
       <c r="AB38" s="8">
-        <v>46153.476168981484</v>
+        <v>46163.43991898148</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD38" s="6" t="s">
-        <v>391</v>
+        <v>93</v>
       </c>
       <c r="AE38" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AF38" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AG38" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AH38" s="6" t="s">
         <v>57</v>
@@ -6576,81 +6648,81 @@
         <v>69</v>
       </c>
       <c r="AJ38" s="6" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AK38" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AL38" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AM38" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AN38" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO38" s="9">
-        <v>45888.833333333336</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP38" s="9">
-        <v>46147.73263888889</v>
+        <v>46174.99998842592</v>
       </c>
       <c r="AQ38" s="6" t="s">
         <v>73</v>
       </c>
       <c r="AR38" s="6" t="s">
-        <v>57</v>
+        <v>394</v>
       </c>
       <c r="AS38" s="6" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AT38" s="6" t="s">
-        <v>356</v>
+        <v>74</v>
       </c>
       <c r="AU38" s="6" t="s">
-        <v>57</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
       <c r="A39" s="7">
-        <v>181781</v>
+        <v>160050</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F39" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="H39" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>400</v>
-      </c>
       <c r="I39" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K39" s="8">
-        <v>46153.47620370371</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>57</v>
+        <v>46160.49762731481</v>
+      </c>
+      <c r="L39" s="9">
+        <v>45832.125</v>
       </c>
       <c r="M39" s="10">
-        <v>53500</v>
+        <v>52700</v>
       </c>
       <c r="N39" s="10">
         <v>0</v>
@@ -6668,10 +6740,10 @@
         <v>0</v>
       </c>
       <c r="S39" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T39" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U39" s="6" t="s">
         <v>60</v>
@@ -6680,13 +6752,13 @@
         <v>57</v>
       </c>
       <c r="W39" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X39" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y39" s="6" t="s">
-        <v>401</v>
+        <v>236</v>
       </c>
       <c r="Z39" s="6" t="s">
         <v>57</v>
@@ -6695,49 +6767,49 @@
         <v>64</v>
       </c>
       <c r="AB39" s="8">
-        <v>46153.47620370371</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD39" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="AE39" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF39" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="AG39" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="AH39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI39" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ39" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="AE39" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="AF39" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG39" s="6" t="s">
+      <c r="AK39" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="AH39" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI39" s="6" t="s">
+      <c r="AL39" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="AJ39" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="AK39" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="AL39" s="6" t="s">
-        <v>407</v>
-      </c>
       <c r="AM39" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AN39" s="6" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="AO39" s="9">
-        <v>45986.458333333336</v>
+        <v>45888.833333333336</v>
       </c>
       <c r="AP39" s="9">
-        <v>46168.458333333336</v>
+        <v>46147.73263888889</v>
       </c>
       <c r="AQ39" s="6" t="s">
         <v>73</v>
@@ -6746,54 +6818,54 @@
         <v>57</v>
       </c>
       <c r="AS39" s="6" t="s">
-        <v>74</v>
+        <v>366</v>
       </c>
       <c r="AT39" s="6" t="s">
-        <v>74</v>
+        <v>366</v>
       </c>
       <c r="AU39" s="6" t="s">
-        <v>356</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
       <c r="A40" s="7">
-        <v>186661</v>
+        <v>181781</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I40" s="8">
-        <v>46154.478113425925</v>
+        <v>46153.47620370371</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="K40" s="8">
-        <v>46154.478113425925</v>
+        <v>46153.47620370371</v>
       </c>
       <c r="L40" s="9" t="s">
         <v>57</v>
       </c>
       <c r="M40" s="10">
-        <v>49500</v>
+        <v>53500</v>
       </c>
       <c r="N40" s="10">
         <v>0</v>
@@ -6811,25 +6883,25 @@
         <v>0</v>
       </c>
       <c r="S40" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T40" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U40" s="6" t="s">
         <v>60</v>
       </c>
       <c r="V40" s="6" t="s">
-        <v>412</v>
+        <v>57</v>
       </c>
       <c r="W40" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X40" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y40" s="6" t="s">
-        <v>96</v>
+        <v>409</v>
       </c>
       <c r="Z40" s="6" t="s">
         <v>57</v>
@@ -6838,49 +6910,49 @@
         <v>64</v>
       </c>
       <c r="AB40" s="8">
-        <v>46154.478113425925</v>
+        <v>46153.47620370371</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD40" s="6" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="AE40" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG40" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="AH40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI40" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="AJ40" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="AF40" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG40" s="6" t="s">
+      <c r="AK40" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="AH40" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI40" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ40" s="6" t="s">
+      <c r="AL40" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="AK40" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="AL40" s="6" t="s">
-        <v>417</v>
-      </c>
       <c r="AM40" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AN40" s="6" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="AO40" s="9">
-        <v>45911.791666666664</v>
+        <v>45986.458333333336</v>
       </c>
       <c r="AP40" s="9">
-        <v>46139.48611111111</v>
+        <v>46168.458333333336</v>
       </c>
       <c r="AQ40" s="6" t="s">
         <v>73</v>
@@ -6895,84 +6967,84 @@
         <v>74</v>
       </c>
       <c r="AU40" s="6" t="s">
-        <v>74</v>
+        <v>366</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
       <c r="A41" s="7">
-        <v>190482</v>
+        <v>186661</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F41" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>421</v>
-      </c>
       <c r="I41" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K41" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="L41" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M41" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N41" s="10" t="s">
-        <v>57</v>
+      <c r="M41" s="10">
+        <v>49500</v>
+      </c>
+      <c r="N41" s="10">
+        <v>0</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P41" s="10" t="s">
-        <v>57</v>
+      <c r="P41" s="10">
+        <v>0</v>
       </c>
       <c r="Q41" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R41" s="10" t="s">
-        <v>57</v>
+      <c r="R41" s="10">
+        <v>0</v>
       </c>
       <c r="S41" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T41" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U41" s="6" t="s">
         <v>60</v>
       </c>
       <c r="V41" s="6" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="W41" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X41" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y41" s="6" t="s">
-        <v>422</v>
+        <v>221</v>
       </c>
       <c r="Z41" s="6" t="s">
         <v>57</v>
@@ -6981,22 +7053,22 @@
         <v>64</v>
       </c>
       <c r="AB41" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.497662037036</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD41" s="6" t="s">
-        <v>212</v>
+        <v>399</v>
       </c>
       <c r="AE41" s="6" t="s">
-        <v>227</v>
+        <v>421</v>
       </c>
       <c r="AF41" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AG41" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AH41" s="6" t="s">
         <v>57</v>
@@ -7005,25 +7077,25 @@
         <v>69</v>
       </c>
       <c r="AJ41" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="AK41" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="AK41" s="6" t="s">
+      <c r="AL41" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="AL41" s="6" t="s">
-        <v>426</v>
-      </c>
       <c r="AM41" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AN41" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO41" s="9">
-        <v>46087.625</v>
+        <v>45911.791666666664</v>
       </c>
       <c r="AP41" s="9">
-        <v>46167.99998842592</v>
+        <v>46139.48611111111</v>
       </c>
       <c r="AQ41" s="6" t="s">
         <v>73</v>
@@ -7038,84 +7110,84 @@
         <v>74</v>
       </c>
       <c r="AU41" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
       <c r="A42" s="7">
-        <v>193485</v>
+        <v>190482</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F42" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>430</v>
-      </c>
       <c r="I42" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K42" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="L42" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M42" s="10">
-        <v>0</v>
-      </c>
-      <c r="N42" s="10">
-        <v>0</v>
+      <c r="M42" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="O42" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P42" s="10">
-        <v>0</v>
+      <c r="P42" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="Q42" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R42" s="10">
-        <v>0</v>
+      <c r="R42" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="S42" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U42" s="6" t="s">
-        <v>332</v>
+        <v>60</v>
       </c>
       <c r="V42" s="6" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="W42" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X42" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y42" s="6" t="s">
-        <v>250</v>
+        <v>430</v>
       </c>
       <c r="Z42" s="6" t="s">
         <v>57</v>
@@ -7124,22 +7196,22 @@
         <v>64</v>
       </c>
       <c r="AB42" s="8">
-        <v>46153.476168981484</v>
+        <v>46160.49762731481</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD42" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="AE42" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF42" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG42" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="AE42" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="AF42" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG42" s="6" t="s">
-        <v>432</v>
       </c>
       <c r="AH42" s="6" t="s">
         <v>57</v>
@@ -7148,25 +7220,25 @@
         <v>69</v>
       </c>
       <c r="AJ42" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="AK42" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="AK42" s="6" t="s">
+      <c r="AL42" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="AL42" s="6" t="s">
-        <v>435</v>
-      </c>
       <c r="AM42" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN42" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO42" s="9">
-        <v>45861.54583333333</v>
+        <v>46087.625</v>
       </c>
       <c r="AP42" s="9">
-        <v>46167.458333333336</v>
+        <v>46167.99998842592</v>
       </c>
       <c r="AQ42" s="6" t="s">
         <v>73</v>
@@ -7181,84 +7253,84 @@
         <v>74</v>
       </c>
       <c r="AU42" s="6" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
       <c r="A43" s="7">
-        <v>194034</v>
+        <v>193485</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F43" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="H43" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>439</v>
-      </c>
       <c r="I43" s="8">
-        <v>46153.47618055555</v>
+        <v>46161.57792824074</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K43" s="8">
-        <v>46153.47618055555</v>
+        <v>46161.57792824074</v>
       </c>
       <c r="L43" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M43" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>57</v>
+      <c r="M43" s="10">
+        <v>0</v>
+      </c>
+      <c r="N43" s="10">
+        <v>0</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P43" s="10" t="s">
-        <v>57</v>
+      <c r="P43" s="10">
+        <v>0</v>
       </c>
       <c r="Q43" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R43" s="10" t="s">
-        <v>57</v>
+      <c r="R43" s="10">
+        <v>0</v>
       </c>
       <c r="S43" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="T43" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U43" s="6" t="s">
-        <v>60</v>
+        <v>342</v>
       </c>
       <c r="V43" s="6" t="s">
         <v>57</v>
       </c>
       <c r="W43" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X43" s="6" t="s">
         <v>62</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>361</v>
+        <v>260</v>
       </c>
       <c r="Z43" s="6" t="s">
         <v>57</v>
@@ -7267,22 +7339,22 @@
         <v>64</v>
       </c>
       <c r="AB43" s="8">
-        <v>46153.47618055555</v>
+        <v>46161.57792824074</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD43" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="AE43" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF43" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG43" s="6" t="s">
         <v>440</v>
-      </c>
-      <c r="AE43" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="AF43" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG43" s="6" t="s">
-        <v>441</v>
       </c>
       <c r="AH43" s="6" t="s">
         <v>57</v>
@@ -7291,16 +7363,16 @@
         <v>69</v>
       </c>
       <c r="AJ43" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK43" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="AK43" s="6" t="s">
+      <c r="AL43" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="AL43" s="6" t="s">
-        <v>444</v>
-      </c>
       <c r="AM43" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AN43" s="6" t="s">
         <v>57</v>
@@ -7309,7 +7381,7 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AP43" s="9">
-        <v>46174.99998842592</v>
+        <v>46167.458333333336</v>
       </c>
       <c r="AQ43" s="6" t="s">
         <v>73</v>
@@ -7318,48 +7390,48 @@
         <v>57</v>
       </c>
       <c r="AS43" s="6" t="s">
-        <v>356</v>
+        <v>74</v>
       </c>
       <c r="AT43" s="6" t="s">
-        <v>356</v>
+        <v>74</v>
       </c>
       <c r="AU43" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
       <c r="A44" s="7">
-        <v>194641</v>
+        <v>194034</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D44" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>449</v>
-      </c>
       <c r="I44" s="8">
-        <v>46100.406643518516</v>
+        <v>46163.39525462963</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K44" s="8">
-        <v>46100.406643518516</v>
+        <v>46163.39525462963</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>57</v>
@@ -7386,7 +7458,7 @@
         <v>249</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="U44" s="6" t="s">
         <v>60</v>
@@ -7395,13 +7467,13 @@
         <v>57</v>
       </c>
       <c r="W44" s="6" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="X44" s="6" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="Y44" s="6" t="s">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="Z44" s="6" t="s">
         <v>57</v>
@@ -7410,22 +7482,22 @@
         <v>64</v>
       </c>
       <c r="AB44" s="8">
-        <v>46100.406643518516</v>
+        <v>46163.39525462963</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD44" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AE44" s="6" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AF44" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AG44" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AH44" s="6" t="s">
         <v>57</v>
@@ -7434,25 +7506,25 @@
         <v>69</v>
       </c>
       <c r="AJ44" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="AK44" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="AL44" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="AK44" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="AL44" s="6" t="s">
-        <v>454</v>
-      </c>
       <c r="AM44" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN44" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO44" s="9">
-        <v>46097.791666666664</v>
+        <v>45861.54583333333</v>
       </c>
       <c r="AP44" s="9">
-        <v>46181.458333333336</v>
+        <v>46174.99998842592</v>
       </c>
       <c r="AQ44" s="6" t="s">
         <v>73</v>
@@ -7461,48 +7533,48 @@
         <v>57</v>
       </c>
       <c r="AS44" s="6" t="s">
-        <v>455</v>
+        <v>366</v>
       </c>
       <c r="AT44" s="6" t="s">
-        <v>455</v>
+        <v>366</v>
       </c>
       <c r="AU44" s="6" t="s">
-        <v>455</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
       <c r="A45" s="7">
-        <v>197996</v>
+        <v>194641</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F45" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>459</v>
-      </c>
       <c r="I45" s="8">
-        <v>46147.625</v>
+        <v>46100.406643518516</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K45" s="8">
-        <v>46147.625</v>
+        <v>46100.406643518516</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>57</v>
@@ -7526,10 +7598,10 @@
         <v>57</v>
       </c>
       <c r="S45" s="6" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="T45" s="6" t="s">
-        <v>460</v>
+        <v>293</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>60</v>
@@ -7544,7 +7616,7 @@
         <v>62</v>
       </c>
       <c r="Y45" s="6" t="s">
-        <v>461</v>
+        <v>381</v>
       </c>
       <c r="Z45" s="6" t="s">
         <v>57</v>
@@ -7553,22 +7625,22 @@
         <v>64</v>
       </c>
       <c r="AB45" s="8">
-        <v>46148.48179398148</v>
+        <v>46100.406643518516</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD45" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AE45" s="6" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AF45" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AG45" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AH45" s="6" t="s">
         <v>57</v>
@@ -7577,25 +7649,25 @@
         <v>69</v>
       </c>
       <c r="AJ45" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AK45" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AL45" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AM45" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AN45" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO45" s="9">
-        <v>46153.75</v>
+        <v>46097.791666666664</v>
       </c>
       <c r="AP45" s="9">
-        <v>46237.99998842592</v>
+        <v>46181.458333333336</v>
       </c>
       <c r="AQ45" s="6" t="s">
         <v>73</v>
@@ -7604,75 +7676,75 @@
         <v>57</v>
       </c>
       <c r="AS45" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AT45" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AU45" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
       <c r="A46" s="7">
-        <v>201183</v>
+        <v>197996</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="I46" s="8">
+        <v>46147.625</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="K46" s="8">
+        <v>46147.625</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O46" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P46" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q46" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R46" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="S46" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="T46" s="6" t="s">
         <v>468</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="I46" s="8">
-        <v>46142.5</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="K46" s="8">
-        <v>46142.5</v>
-      </c>
-      <c r="L46" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M46" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N46" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O46" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P46" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q46" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R46" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="S46" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="T46" s="6" t="s">
-        <v>474</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>60</v>
@@ -7687,31 +7759,31 @@
         <v>62</v>
       </c>
       <c r="Y46" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="Z46" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AA46" s="6" t="s">
-        <v>475</v>
+        <v>64</v>
       </c>
       <c r="AB46" s="8">
-        <v>46148.466678240744</v>
+        <v>46148.48179398148</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD46" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AE46" s="6" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AF46" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AG46" s="6" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AH46" s="6" t="s">
         <v>57</v>
@@ -7720,25 +7792,25 @@
         <v>69</v>
       </c>
       <c r="AJ46" s="6" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AK46" s="6" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="AL46" s="6" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AM46" s="6" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AN46" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AO46" s="9">
-        <v>46142.625</v>
+        <v>46153.75</v>
       </c>
       <c r="AP46" s="9">
-        <v>46223.99998842592</v>
+        <v>46237.99998842592</v>
       </c>
       <c r="AQ46" s="6" t="s">
         <v>73</v>
@@ -7747,75 +7819,75 @@
         <v>57</v>
       </c>
       <c r="AS46" s="6" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="AT46" s="6" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="AU46" s="6" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
       <c r="A47" s="7">
-        <v>201185</v>
+        <v>201183</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="I47" s="8">
+        <v>46142.5</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="K47" s="8">
+        <v>46142.5</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O47" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q47" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R47" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="S47" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="F47" s="6" t="s">
+      <c r="T47" s="6" t="s">
         <v>482</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="I47" s="8">
-        <v>46147.625</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="K47" s="8">
-        <v>46147.625</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q47" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R47" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="S47" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="T47" s="6" t="s">
-        <v>474</v>
       </c>
       <c r="U47" s="6" t="s">
         <v>60</v>
@@ -7830,25 +7902,25 @@
         <v>62</v>
       </c>
       <c r="Y47" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="Z47" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AA47" s="6" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="AB47" s="8">
-        <v>46148.45706018519</v>
+        <v>46148.466678240744</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD47" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AE47" s="6" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AF47" s="6" t="s">
         <v>57</v>
@@ -7878,10 +7950,10 @@
         <v>57</v>
       </c>
       <c r="AO47" s="9">
-        <v>46147.75</v>
+        <v>46142.625</v>
       </c>
       <c r="AP47" s="9">
-        <v>46230.99998842592</v>
+        <v>46223.99998842592</v>
       </c>
       <c r="AQ47" s="6" t="s">
         <v>73</v>
@@ -7890,48 +7962,48 @@
         <v>57</v>
       </c>
       <c r="AS47" s="6" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AT47" s="6" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AU47" s="6" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
       <c r="A48" s="7">
-        <v>202468</v>
+        <v>201184</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>51</v>
+        <v>475</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="G48" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="H48" s="6" t="s">
-        <v>493</v>
-      </c>
       <c r="I48" s="8">
-        <v>46150.583333333336</v>
+        <v>46154.333333333336</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K48" s="8">
-        <v>46150.583333333336</v>
+        <v>46154.333333333336</v>
       </c>
       <c r="L48" s="9" t="s">
         <v>57</v>
@@ -7955,10 +8027,10 @@
         <v>57</v>
       </c>
       <c r="S48" s="6" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="T48" s="6" t="s">
-        <v>81</v>
+        <v>482</v>
       </c>
       <c r="U48" s="6" t="s">
         <v>60</v>
@@ -7973,31 +8045,31 @@
         <v>62</v>
       </c>
       <c r="Y48" s="6" t="s">
-        <v>495</v>
+        <v>80</v>
       </c>
       <c r="Z48" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AA48" s="6" t="s">
-        <v>64</v>
+        <v>483</v>
       </c>
       <c r="AB48" s="8">
-        <v>46153.46357638889</v>
+        <v>46160.41605324074</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD48" s="6" t="s">
-        <v>495</v>
+        <v>80</v>
       </c>
       <c r="AE48" s="6" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AF48" s="6" t="s">
         <v>57</v>
       </c>
       <c r="AG48" s="6" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AH48" s="6" t="s">
         <v>57</v>
@@ -8006,25 +8078,25 @@
         <v>69</v>
       </c>
       <c r="AJ48" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="AK48" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="AL48" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="AM48" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="AN48" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="AK48" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="AL48" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="AM48" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="AN48" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="AO48" s="9">
-        <v>46150.67013888889</v>
+        <v>46154.458333333336</v>
       </c>
       <c r="AP48" s="9">
-        <v>46230.99998842592</v>
+        <v>46237.99998842592</v>
       </c>
       <c r="AQ48" s="6" t="s">
         <v>73</v>
@@ -8033,155 +8105,584 @@
         <v>57</v>
       </c>
       <c r="AS48" s="6" t="s">
-        <v>57</v>
+        <v>488</v>
       </c>
       <c r="AT48" s="6" t="s">
-        <v>57</v>
+        <v>488</v>
       </c>
       <c r="AU48" s="6" t="s">
-        <v>74</v>
+        <v>488</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
-      <c r="A49" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I49" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="K49" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="L49" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="M49" s="15">
-        <f>SUM(M6:M48)</f>
-      </c>
-      <c r="N49" s="15">
-        <f>SUM(N6:N48)</f>
-      </c>
-      <c r="O49" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="P49" s="15">
-        <f>SUM(P6:P48)</f>
-      </c>
-      <c r="Q49" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="R49" s="15">
-        <f>SUM(R6:R48)</f>
-      </c>
-      <c r="S49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="T49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="U49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="V49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="W49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="X49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB49" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AK49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AM49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AO49" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="AP49" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="AQ49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AR49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AU49" s="12" t="s">
+      <c r="A49" s="7">
+        <v>201185</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="I49" s="8">
+        <v>46147.625</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="K49" s="8">
+        <v>46147.625</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q49" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R49" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="S49" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="T49" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="U49" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="V49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="W49" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="X49" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y49" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA49" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="AB49" s="8">
+        <v>46148.45706018519</v>
+      </c>
+      <c r="AC49" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD49" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="AE49" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG49" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI49" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ49" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="AK49" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="AL49" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="AM49" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="AN49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO49" s="9">
+        <v>46147.75</v>
+      </c>
+      <c r="AP49" s="9">
+        <v>46230.99998842592</v>
+      </c>
+      <c r="AQ49" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS49" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="AT49" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="AU49" s="6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="50" ht="23" customHeight="1">
+      <c r="A50" s="7">
+        <v>201186</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="I50" s="8">
+        <v>46158.333333333336</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="K50" s="8">
+        <v>46158.333333333336</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M50" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N50" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O50" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q50" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R50" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="S50" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="T50" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="U50" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="V50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="W50" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="X50" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y50" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA50" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>46160.42208333333</v>
+      </c>
+      <c r="AC50" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD50" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE50" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG50" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="AH50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI50" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ50" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="AK50" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="AL50" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="AM50" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="AN50" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="AO50" s="9">
+        <v>46158.458333333336</v>
+      </c>
+      <c r="AP50" s="9">
+        <v>46237.99998842592</v>
+      </c>
+      <c r="AQ50" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS50" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="AT50" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="AU50" s="6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="51" ht="23" customHeight="1">
+      <c r="A51" s="7">
+        <v>202468</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="I51" s="8">
+        <v>46150.583333333336</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="K51" s="8">
+        <v>46150.583333333336</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q51" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R51" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="S51" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="T51" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="U51" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="V51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="W51" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="X51" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y51" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="Z51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA51" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>46153.46357638889</v>
+      </c>
+      <c r="AC51" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD51" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="AE51" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG51" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="AH51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI51" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ51" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="AK51" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="AL51" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="AM51" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="AN51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO51" s="9">
+        <v>46150.67013888889</v>
+      </c>
+      <c r="AP51" s="9">
+        <v>46230.99998842592</v>
+      </c>
+      <c r="AQ51" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AT51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU51" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" ht="23" customHeight="1">
+      <c r="A52" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M52" s="15">
+        <f>SUM(M6:M51)</f>
+      </c>
+      <c r="N52" s="15">
+        <f>SUM(N6:N51)</f>
+      </c>
+      <c r="O52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="P52" s="15">
+        <f>SUM(P6:P51)</f>
+      </c>
+      <c r="Q52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="R52" s="15">
+        <f>SUM(R6:R51)</f>
+      </c>
+      <c r="S52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="T52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="U52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="V52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="W52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="X52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB52" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AT52" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU52" s="12" t="s">
         <v>57</v>
       </c>
     </row>
